--- a/database/event/1615/event_1615_evp_summary.xlsx
+++ b/database/event/1615/event_1615_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9443</v>
+        <v>6.5094</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4673</v>
+        <v>3.7969</v>
       </c>
       <c r="D2" t="n">
-        <v>1.98</v>
+        <v>2.1494</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9443</v>
+        <v>6.5094</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1788</v>
+        <v>2.7439</v>
       </c>
       <c r="G2" t="n">
         <v>3.7655</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1788</v>
+        <v>2.7439</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7659</v>
+        <v>2.224</v>
       </c>
       <c r="J2" t="n">
         <v>3.7655</v>
@@ -529,7 +529,7 @@
         <v>153</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5314</v>
+        <v>5.9895</v>
       </c>
       <c r="N2" t="n">
         <v>189</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5368</v>
+        <v>4.4395</v>
       </c>
       <c r="C3" t="n">
-        <v>2.063</v>
+        <v>2.5896</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0074</v>
+        <v>1.3248</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5368</v>
+        <v>4.4395</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7489</v>
+        <v>3.6516</v>
       </c>
       <c r="G3" t="n">
         <v>0.7879</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7489</v>
+        <v>3.6516</v>
       </c>
       <c r="I3" t="n">
-        <v>2.228</v>
+        <v>2.9597</v>
       </c>
       <c r="J3" t="n">
         <v>0.7879</v>
@@ -575,7 +575,7 @@
         <v>153</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0159</v>
+        <v>3.7476</v>
       </c>
       <c r="N3" t="n">
         <v>189</v>
@@ -594,7 +594,7 @@
         <v>1.8563</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8643</v>
+        <v>0.824</v>
       </c>
       <c r="E4" t="n">
         <v>3.1824</v>
@@ -640,7 +640,7 @@
         <v>1.8336</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8485</v>
+        <v>0.8085</v>
       </c>
       <c r="E5" t="n">
         <v>3.1435</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.2153</v>
+        <v>2.5612</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2922</v>
+        <v>1.4939</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4736</v>
+        <v>0.5765</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2153</v>
+        <v>2.5612</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0743</v>
+        <v>3.2384</v>
       </c>
       <c r="G6" t="n">
-        <v>0.141</v>
+        <v>-0.6772</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0743</v>
+        <v>3.2384</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6813</v>
+        <v>2.6248</v>
       </c>
       <c r="J6" t="n">
-        <v>0.141</v>
+        <v>-0.6772</v>
       </c>
       <c r="K6" t="n">
-        <v>177</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8223</v>
+        <v>1.9476</v>
       </c>
       <c r="N6" t="n">
-        <v>333</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.9657</v>
+        <v>2.4125</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1466</v>
+        <v>1.4072</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3727</v>
+        <v>0.5172</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9657</v>
+        <v>2.4125</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1995</v>
+        <v>2.6463</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2338</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1995</v>
+        <v>2.6463</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7828</v>
+        <v>2.1449</v>
       </c>
       <c r="J7" t="n">
         <v>-0.2338</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>1.549</v>
+        <v>1.9111</v>
       </c>
       <c r="N7" t="n">
         <v>126</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.9609</v>
+        <v>2.2153</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1438</v>
+        <v>1.2922</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3708</v>
+        <v>0.4387</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9609</v>
+        <v>2.2153</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6381</v>
+        <v>2.0743</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6772</v>
+        <v>0.141</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6381</v>
+        <v>2.0743</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1382</v>
+        <v>1.6813</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6772</v>
+        <v>0.141</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="L8" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M8" t="n">
-        <v>1.461</v>
+        <v>1.8223</v>
       </c>
       <c r="N8" t="n">
-        <v>189</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.3938</v>
+        <v>1.6683</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.9731</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1417</v>
+        <v>0.2207</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3938</v>
+        <v>1.6683</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3938</v>
+        <v>1.6683</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3938</v>
+        <v>1.6683</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3938</v>
+        <v>1.6683</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3938</v>
+        <v>1.6683</v>
       </c>
       <c r="N9" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.325</v>
+        <v>1.4124</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7729</v>
+        <v>0.8239</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1139</v>
+        <v>0.1188</v>
       </c>
       <c r="E10" t="n">
-        <v>1.325</v>
+        <v>1.4124</v>
       </c>
       <c r="F10" t="n">
-        <v>1.325</v>
+        <v>1.4124</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.325</v>
+        <v>1.4124</v>
       </c>
       <c r="I10" t="n">
-        <v>1.325</v>
+        <v>1.4124</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.325</v>
+        <v>1.4124</v>
       </c>
       <c r="N10" t="n">
         <v>132</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3165</v>
+        <v>1.3938</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7679</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1105</v>
+        <v>0.1114</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3165</v>
+        <v>1.3938</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7371</v>
+        <v>1.3938</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4206</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7371</v>
+        <v>1.3938</v>
       </c>
       <c r="I11" t="n">
-        <v>1.408</v>
+        <v>1.3938</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4206</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L11" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9873999999999999</v>
+        <v>1.3938</v>
       </c>
       <c r="N11" t="n">
-        <v>181</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.1885</v>
+        <v>1.3887</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6933</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0588</v>
+        <v>0.1093</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1885</v>
+        <v>1.3887</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1885</v>
+        <v>1.8093</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.4206</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1885</v>
+        <v>1.8093</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1885</v>
+        <v>1.4665</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.4206</v>
       </c>
       <c r="K12" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1885</v>
+        <v>1.0459</v>
       </c>
       <c r="N12" t="n">
-        <v>132</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13">
@@ -1008,7 +1008,7 @@
         <v>0.6847</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0528</v>
+        <v>0.0237</v>
       </c>
       <c r="E13" t="n">
         <v>1.1738</v>
@@ -1054,7 +1054,7 @@
         <v>0.4215</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1294</v>
+        <v>-0.156</v>
       </c>
       <c r="E14" t="n">
         <v>0.7226</v>
@@ -1090,173 +1090,173 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5391</v>
+        <v>0.7058</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3145</v>
+        <v>0.4117</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2036</v>
+        <v>-0.1627</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5391</v>
+        <v>0.7058</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5391</v>
+        <v>1.69</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.9842</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5391</v>
+        <v>1.69</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5391</v>
+        <v>1.3698</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.9842</v>
       </c>
       <c r="K15" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5391</v>
+        <v>0.3855999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4793</v>
+        <v>0.5391</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2796</v>
+        <v>0.3145</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2277</v>
+        <v>-0.2291</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4793</v>
+        <v>0.5391</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3746</v>
+        <v>0.5391</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8539</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3746</v>
+        <v>0.5391</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3036</v>
+        <v>0.5391</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8539</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="L16" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5503</v>
+        <v>0.5391</v>
       </c>
       <c r="N16" t="n">
-        <v>333</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2694</v>
+        <v>0.4793</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1571</v>
+        <v>0.2796</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3125</v>
+        <v>-0.253</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2694</v>
+        <v>0.4793</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7344000000000001</v>
+        <v>-0.3746</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.465</v>
+        <v>0.8539</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7344000000000001</v>
+        <v>-0.3746</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5952</v>
+        <v>-0.3036</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.465</v>
+        <v>0.8539</v>
       </c>
       <c r="K17" t="n">
-        <v>45</v>
+        <v>177</v>
       </c>
       <c r="L17" t="n">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1301999999999999</v>
+        <v>0.5503</v>
       </c>
       <c r="N17" t="n">
-        <v>126</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1407</v>
+        <v>0.4777</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.2786</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3645</v>
+        <v>-0.2536</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1407</v>
+        <v>0.4777</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1249</v>
+        <v>0.9427</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9842</v>
+        <v>-0.465</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1249</v>
+        <v>0.9427</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9117</v>
+        <v>0.7641</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9842</v>
+        <v>-0.465</v>
       </c>
       <c r="K18" t="n">
         <v>45</v>
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.07250000000000001</v>
+        <v>0.2991</v>
       </c>
       <c r="N18" t="n">
         <v>126</v>
@@ -1284,7 +1284,7 @@
         <v>0.0678</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3744</v>
+        <v>-0.3976</v>
       </c>
       <c r="E19" t="n">
         <v>0.1163</v>
@@ -1330,7 +1330,7 @@
         <v>0.0631</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3777</v>
+        <v>-0.4008</v>
       </c>
       <c r="E20" t="n">
         <v>0.1082</v>
@@ -1376,7 +1376,7 @@
         <v>0.0188</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4083</v>
+        <v>-0.431</v>
       </c>
       <c r="E21" t="n">
         <v>0.0323</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.046</v>
+        <v>0.0282</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0268</v>
+        <v>0.0164</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4399</v>
+        <v>-0.4327</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.046</v>
+        <v>0.0282</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2984</v>
+        <v>0.1617</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2524</v>
+        <v>-0.1335</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2984</v>
+        <v>0.1617</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2419</v>
+        <v>0.1311</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2524</v>
+        <v>-0.1335</v>
       </c>
       <c r="K22" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="L22" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01050000000000001</v>
+        <v>-0.002400000000000013</v>
       </c>
       <c r="N22" t="n">
-        <v>126</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1813</v>
+        <v>-0.046</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1058</v>
+        <v>-0.0268</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4946</v>
+        <v>-0.4622</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1813</v>
+        <v>-0.046</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8187</v>
+        <v>-0.2984</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0.2524</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8187</v>
+        <v>-0.2984</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6636</v>
+        <v>-0.2419</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0.2524</v>
       </c>
       <c r="K23" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="L23" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3364</v>
+        <v>0.01050000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>181</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ofnu</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2755</v>
+        <v>-0.1382</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1607</v>
+        <v>-0.0806</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5327</v>
+        <v>-0.499</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2755</v>
+        <v>-0.1382</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2755</v>
+        <v>0.8618</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2755</v>
+        <v>0.8618</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2755</v>
+        <v>0.6985</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2755</v>
+        <v>-0.3015</v>
       </c>
       <c r="N24" t="n">
-        <v>79</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>ofnu</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3062</v>
+        <v>-0.2755</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1786</v>
+        <v>-0.1607</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5451</v>
+        <v>-0.5537</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3062</v>
+        <v>-0.2755</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1727</v>
+        <v>-0.2755</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1335</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1727</v>
+        <v>-0.2755</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.14</v>
+        <v>-0.2755</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1335</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="L25" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2735</v>
+        <v>-0.2755</v>
       </c>
       <c r="N25" t="n">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -1606,7 +1606,7 @@
         <v>-0.2134</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5692</v>
+        <v>-0.5897</v>
       </c>
       <c r="E26" t="n">
         <v>-0.3659</v>
@@ -1652,7 +1652,7 @@
         <v>-0.3198</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6428</v>
+        <v>-0.6623</v>
       </c>
       <c r="E27" t="n">
         <v>-0.5482</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.7151</v>
+        <v>-0.6539</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.4171</v>
+        <v>-0.3814</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.7044</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7151</v>
+        <v>-0.6539</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7151</v>
+        <v>-0.6539</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7151</v>
+        <v>-0.6539</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7151</v>
+        <v>-0.6539</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.7151</v>
+        <v>-0.6539</v>
       </c>
       <c r="N28" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>busta</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7151</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4319</v>
+        <v>-0.4171</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7205</v>
+        <v>-0.7288</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7151</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7151</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7151</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7151</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7151</v>
       </c>
       <c r="N29" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>busta</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7718</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4502</v>
+        <v>-0.4319</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7332</v>
+        <v>-0.7389</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7718</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7718</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7718</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7718</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7718</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
@@ -1836,7 +1836,7 @@
         <v>-0.4718</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7481</v>
+        <v>-0.7662</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8089</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4892</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7601</v>
+        <v>-0.778</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8386</v>
@@ -1928,7 +1928,7 @@
         <v>-0.5317</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7896</v>
+        <v>-0.8071</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9116</v>
@@ -1974,7 +1974,7 @@
         <v>-0.6561</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8758</v>
+        <v>-0.892</v>
       </c>
       <c r="E34" t="n">
         <v>-1.1248</v>
@@ -2020,7 +2020,7 @@
         <v>-0.6917</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9004</v>
+        <v>-0.9164</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1859</v>
@@ -2066,7 +2066,7 @@
         <v>-0.7776999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.96</v>
+        <v>-0.9751</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3333</v>
@@ -2112,7 +2112,7 @@
         <v>-0.8628</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0189</v>
+        <v>-1.0332</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4792</v>
@@ -2158,7 +2158,7 @@
         <v>-0.9134</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.054</v>
+        <v>-1.0678</v>
       </c>
       <c r="E38" t="n">
         <v>-1.566</v>
@@ -2204,7 +2204,7 @@
         <v>-1.0993</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1827</v>
+        <v>-1.1947</v>
       </c>
       <c r="E39" t="n">
         <v>-1.8846</v>
@@ -2250,7 +2250,7 @@
         <v>-1.2587</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2931</v>
+        <v>-1.3036</v>
       </c>
       <c r="E40" t="n">
         <v>-2.1579</v>
@@ -2296,7 +2296,7 @@
         <v>-1.7004</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.599</v>
+        <v>-1.6053</v>
       </c>
       <c r="E41" t="n">
         <v>-2.9151</v>

--- a/database/event/1615/event_1615_evp_summary.xlsx
+++ b/database/event/1615/event_1615_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5094</v>
+        <v>5.8236</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7969</v>
+        <v>3.3969</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1494</v>
+        <v>1.9911</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5094</v>
+        <v>5.8236</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7439</v>
+        <v>2.7138</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7655</v>
+        <v>3.1097</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7439</v>
+        <v>4.0756</v>
       </c>
       <c r="I2" t="n">
-        <v>2.224</v>
+        <v>2.1191</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7655</v>
+        <v>3.1097</v>
       </c>
       <c r="K2" t="n">
         <v>36</v>
@@ -529,7 +529,7 @@
         <v>153</v>
       </c>
       <c r="M2" t="n">
-        <v>5.9895</v>
+        <v>5.2288</v>
       </c>
       <c r="N2" t="n">
         <v>189</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.4395</v>
+        <v>3.7083</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5896</v>
+        <v>2.163</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3248</v>
+        <v>1.0361</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4395</v>
+        <v>3.7083</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6516</v>
+        <v>3.0215</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7879</v>
+        <v>0.6868</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6516</v>
+        <v>5.1597</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9597</v>
+        <v>2.6828</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7879</v>
+        <v>0.6868</v>
       </c>
       <c r="K3" t="n">
         <v>36</v>
@@ -575,7 +575,7 @@
         <v>153</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7476</v>
+        <v>3.3696</v>
       </c>
       <c r="N3" t="n">
         <v>189</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.1824</v>
+        <v>3.6755</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8563</v>
+        <v>2.1439</v>
       </c>
       <c r="D4" t="n">
-        <v>0.824</v>
+        <v>1.0213</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1824</v>
+        <v>3.6755</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2236</v>
+        <v>2.6122</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9588</v>
+        <v>1.0633</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2236</v>
+        <v>3.7174</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8023</v>
+        <v>1.9329</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9588</v>
+        <v>1.0633</v>
       </c>
       <c r="K4" t="n">
         <v>177</v>
@@ -621,7 +621,7 @@
         <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7611</v>
+        <v>2.9962</v>
       </c>
       <c r="N4" t="n">
         <v>333</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1435</v>
+        <v>3.5164</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8336</v>
+        <v>2.0511</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8085</v>
+        <v>0.9495</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1435</v>
+        <v>3.5164</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6438</v>
+        <v>2.9868</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4997</v>
+        <v>0.5296</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6438</v>
+        <v>5.0372</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1429</v>
+        <v>2.6191</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4997</v>
+        <v>0.5296</v>
       </c>
       <c r="K5" t="n">
         <v>103</v>
@@ -667,7 +667,7 @@
         <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6426</v>
+        <v>3.1487</v>
       </c>
       <c r="N5" t="n">
         <v>181</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5612</v>
+        <v>3.007</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4939</v>
+        <v>1.754</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5765</v>
+        <v>0.7195</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5612</v>
+        <v>3.007</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2384</v>
+        <v>2.6727</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6772</v>
+        <v>0.3343</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2384</v>
+        <v>3.9307</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6248</v>
+        <v>2.0438</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6772</v>
+        <v>0.3343</v>
       </c>
       <c r="K6" t="n">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="L6" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9476</v>
+        <v>2.3781</v>
       </c>
       <c r="N6" t="n">
-        <v>189</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4125</v>
+        <v>2.521</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4072</v>
+        <v>1.4705</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5172</v>
+        <v>0.5001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4125</v>
+        <v>2.521</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6463</v>
+        <v>2.6413</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2338</v>
+        <v>-0.1203</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6463</v>
+        <v>3.82</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1449</v>
+        <v>1.9862</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2338</v>
+        <v>-0.1203</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9111</v>
+        <v>1.8659</v>
       </c>
       <c r="N7" t="n">
         <v>126</v>
@@ -768,124 +768,124 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2153</v>
+        <v>2.2184</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2922</v>
+        <v>1.294</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4387</v>
+        <v>0.3635</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2153</v>
+        <v>2.2184</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0743</v>
+        <v>2.4534</v>
       </c>
       <c r="G8" t="n">
-        <v>0.141</v>
+        <v>-0.235</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0743</v>
+        <v>3.1578</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6813</v>
+        <v>1.6419</v>
       </c>
       <c r="J8" t="n">
-        <v>0.141</v>
+        <v>-0.235</v>
       </c>
       <c r="K8" t="n">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="L8" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8223</v>
+        <v>1.4069</v>
       </c>
       <c r="N8" t="n">
-        <v>333</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.6683</v>
+        <v>2.2016</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9731</v>
+        <v>1.2842</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2207</v>
+        <v>0.3559</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6683</v>
+        <v>2.2016</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6683</v>
+        <v>2.9083</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.7067</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6683</v>
+        <v>4.7609</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6683</v>
+        <v>2.4754</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.7067</v>
       </c>
       <c r="K9" t="n">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6683</v>
+        <v>1.7687</v>
       </c>
       <c r="N9" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.4124</v>
+        <v>1.7088</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8239</v>
+        <v>0.9967</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1188</v>
+        <v>0.1334</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4124</v>
+        <v>1.7088</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4124</v>
+        <v>1.7088</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4124</v>
+        <v>1.7088</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4124</v>
+        <v>1.7088</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4124</v>
+        <v>1.7088</v>
       </c>
       <c r="N10" t="n">
         <v>132</v>
@@ -906,124 +906,124 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3938</v>
+        <v>1.5878</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.9262</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1114</v>
+        <v>0.0788</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3938</v>
+        <v>1.5878</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3938</v>
+        <v>1.5878</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3938</v>
+        <v>1.5878</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3938</v>
+        <v>1.5878</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3938</v>
+        <v>1.5878</v>
       </c>
       <c r="N11" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3887</v>
+        <v>1.5714</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9166</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1093</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3887</v>
+        <v>1.5714</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8093</v>
+        <v>2.2307</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4206</v>
+        <v>-0.6593</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8093</v>
+        <v>2.3733</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4665</v>
+        <v>1.234</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4206</v>
+        <v>-0.6593</v>
       </c>
       <c r="K12" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="L12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0459</v>
+        <v>0.5747</v>
       </c>
       <c r="N12" t="n">
-        <v>181</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1738</v>
+        <v>1.4264</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6847</v>
+        <v>0.832</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0237</v>
+        <v>0.0059</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1738</v>
+        <v>1.4264</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1738</v>
+        <v>1.4264</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1738</v>
+        <v>1.4264</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1738</v>
+        <v>1.4264</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1738</v>
+        <v>1.4264</v>
       </c>
       <c r="N13" t="n">
         <v>97</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7226</v>
+        <v>1.4219</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4215</v>
+        <v>0.8294</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.156</v>
+        <v>0.0039</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7226</v>
+        <v>1.4219</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.709</v>
+        <v>2.0948</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4316</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.709</v>
+        <v>2.0948</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5747</v>
+        <v>1.0892</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4316</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="L14" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8569</v>
+        <v>0.4162999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>333</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7058</v>
+        <v>1.3952</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4117</v>
+        <v>0.8138</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1627</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7058</v>
+        <v>1.3952</v>
       </c>
       <c r="F15" t="n">
-        <v>1.69</v>
+        <v>1.6711</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9842</v>
+        <v>-0.2759</v>
       </c>
       <c r="H15" t="n">
-        <v>1.69</v>
+        <v>1.6711</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3698</v>
+        <v>0.8689</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9842</v>
+        <v>-0.2759</v>
       </c>
       <c r="K15" t="n">
         <v>45</v>
@@ -1127,7 +1127,7 @@
         <v>81</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3855999999999999</v>
+        <v>0.593</v>
       </c>
       <c r="N15" t="n">
         <v>126</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5391</v>
+        <v>1.24</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3145</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2291</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5391</v>
+        <v>1.24</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5391</v>
+        <v>0.47</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5391</v>
+        <v>0.47</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5391</v>
+        <v>0.2444</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="K16" t="n">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5391</v>
+        <v>1.0144</v>
       </c>
       <c r="N16" t="n">
-        <v>113</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4793</v>
+        <v>1.2113</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2796</v>
+        <v>0.7066</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.253</v>
+        <v>-0.0912</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4793</v>
+        <v>1.2113</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3746</v>
+        <v>1.2113</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8539</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3746</v>
+        <v>1.2113</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3036</v>
+        <v>1.2113</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8539</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="L17" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5503</v>
+        <v>1.2113</v>
       </c>
       <c r="N17" t="n">
-        <v>333</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4777</v>
+        <v>1.0894</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2786</v>
+        <v>0.6354</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2536</v>
+        <v>-0.1462</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4777</v>
+        <v>1.0894</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9427</v>
+        <v>1.0894</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.465</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9427</v>
+        <v>1.0894</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7641</v>
+        <v>1.0894</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.465</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="L18" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2991</v>
+        <v>1.0894</v>
       </c>
       <c r="N18" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1163</v>
+        <v>1.0215</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0678</v>
+        <v>0.5958</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3976</v>
+        <v>-0.1769</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1163</v>
+        <v>1.0215</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4047</v>
+        <v>1.1511</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2884</v>
+        <v>-0.1296</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4047</v>
+        <v>1.1511</v>
       </c>
       <c r="I19" t="n">
-        <v>0.328</v>
+        <v>0.5985</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2884</v>
+        <v>-0.1296</v>
       </c>
       <c r="K19" t="n">
         <v>103</v>
@@ -1311,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03960000000000002</v>
+        <v>0.4689</v>
       </c>
       <c r="N19" t="n">
         <v>181</v>
@@ -1320,32 +1320,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1082</v>
+        <v>0.8929</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0631</v>
+        <v>0.5208</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4008</v>
+        <v>-0.2349</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1082</v>
+        <v>0.8929</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1082</v>
+        <v>0.8929</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1082</v>
+        <v>0.8929</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1082</v>
+        <v>0.8929</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1082</v>
+        <v>0.8929</v>
       </c>
       <c r="N20" t="n">
         <v>113</v>
@@ -1366,645 +1366,645 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0323</v>
+        <v>0.7906</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0188</v>
+        <v>0.4612</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.431</v>
+        <v>-0.2811</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0323</v>
+        <v>0.7906</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6065</v>
+        <v>-0.4164</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6388</v>
+        <v>1.207</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6065</v>
+        <v>-0.4164</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4916</v>
+        <v>-0.2165</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6388</v>
+        <v>1.207</v>
       </c>
       <c r="K21" t="n">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="L21" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1472000000000001</v>
+        <v>0.9905</v>
       </c>
       <c r="N21" t="n">
-        <v>189</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0282</v>
+        <v>0.6</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0164</v>
+        <v>0.35</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4327</v>
+        <v>-0.3671</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0282</v>
+        <v>0.6</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1617</v>
+        <v>1.5723</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1335</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1617</v>
+        <v>1.5723</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1311</v>
+        <v>0.8175</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1335</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="L22" t="n">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.002400000000000013</v>
+        <v>-0.1548</v>
       </c>
       <c r="N22" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.046</v>
+        <v>0.3661</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0268</v>
+        <v>0.2135</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4622</v>
+        <v>-0.4727</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.046</v>
+        <v>0.3661</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2984</v>
+        <v>0.2981</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2524</v>
+        <v>0.068</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2984</v>
+        <v>0.2981</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2419</v>
+        <v>0.155</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2524</v>
+        <v>0.068</v>
       </c>
       <c r="K23" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="L23" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01050000000000001</v>
+        <v>0.223</v>
       </c>
       <c r="N23" t="n">
-        <v>126</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>ofnu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1382</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0806</v>
+        <v>0.0051</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.499</v>
+        <v>-0.6341</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1382</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8618</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8618</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6985</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="L24" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3015</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ofnu</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2755</v>
+        <v>-0.0934</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1607</v>
+        <v>-0.0545</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5537</v>
+        <v>-0.6802</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2755</v>
+        <v>-0.0934</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2755</v>
+        <v>-0.0934</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2755</v>
+        <v>-0.0934</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2755</v>
+        <v>-0.0934</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2755</v>
+        <v>-0.0934</v>
       </c>
       <c r="N25" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3659</v>
+        <v>-0.1018</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2134</v>
+        <v>-0.0594</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5897</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3659</v>
+        <v>-0.1018</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7422</v>
+        <v>-0.1018</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.1081</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7422</v>
+        <v>-0.1018</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6016</v>
+        <v>-0.1018</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.1081</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="L26" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5065000000000001</v>
+        <v>-0.1018</v>
       </c>
       <c r="N26" t="n">
-        <v>189</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.5482</v>
+        <v>-0.1056</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3198</v>
+        <v>-0.0616</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6623</v>
+        <v>-0.6857</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5482</v>
+        <v>-0.1056</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5482</v>
+        <v>-0.2406</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5482</v>
+        <v>-0.2406</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5482</v>
+        <v>-0.1251</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="K27" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.5482</v>
+        <v>0.00990000000000002</v>
       </c>
       <c r="N27" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6539</v>
+        <v>-0.2006</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3814</v>
+        <v>-0.117</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7044</v>
+        <v>-0.7286</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6539</v>
+        <v>-0.2006</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6539</v>
+        <v>-0.2006</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6539</v>
+        <v>-0.2006</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6539</v>
+        <v>-0.2006</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6539</v>
+        <v>-0.2006</v>
       </c>
       <c r="N28" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7151</v>
+        <v>-0.246</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4171</v>
+        <v>-0.1435</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7288</v>
+        <v>-0.7491</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7151</v>
+        <v>-0.246</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7151</v>
+        <v>-0.7474</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.5014</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7151</v>
+        <v>-0.7474</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7151</v>
+        <v>-0.3886</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.5014</v>
       </c>
       <c r="K29" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7151</v>
+        <v>0.1128</v>
       </c>
       <c r="N29" t="n">
-        <v>113</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>busta</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.309</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4319</v>
+        <v>-0.1802</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7389</v>
+        <v>-0.7775</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.309</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.309</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.309</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.309</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.309</v>
       </c>
       <c r="N30" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>busta</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8089</v>
+        <v>-0.3649</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.4718</v>
+        <v>-0.2128</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7662</v>
+        <v>-0.8027</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8089</v>
+        <v>-0.3649</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3522</v>
+        <v>-0.3649</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4567</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3522</v>
+        <v>-0.3649</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2855</v>
+        <v>-0.3649</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4567</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="L31" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7422</v>
+        <v>-0.3649</v>
       </c>
       <c r="N31" t="n">
-        <v>126</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>RaZ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8386</v>
+        <v>-0.6726</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4892</v>
+        <v>-0.3923</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.778</v>
+        <v>-0.9417</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8386</v>
+        <v>-0.6726</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8386</v>
+        <v>-0.6726</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8386</v>
+        <v>-0.6726</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8386</v>
+        <v>-0.6726</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8386</v>
+        <v>-0.6726</v>
       </c>
       <c r="N32" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RaZ</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9116</v>
+        <v>-0.6879</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.5317</v>
+        <v>-0.4013</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8071</v>
+        <v>-0.9486</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9116</v>
+        <v>-0.6879</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9116</v>
+        <v>-0.6879</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9116</v>
+        <v>-0.6879</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9116</v>
+        <v>-0.6879</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9116</v>
+        <v>-0.6879</v>
       </c>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1248</v>
+        <v>-0.7099</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.6561</v>
+        <v>-0.4141</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.892</v>
+        <v>-0.9585</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1248</v>
+        <v>-0.7099</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1248</v>
+        <v>-0.4775</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.2324</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.1248</v>
+        <v>-0.4775</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.1248</v>
+        <v>-0.2483</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.2324</v>
       </c>
       <c r="K34" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.1248</v>
+        <v>-0.4807</v>
       </c>
       <c r="N34" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1859</v>
+        <v>-0.8349</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6917</v>
+        <v>-0.487</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9164</v>
+        <v>-1.0149</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1859</v>
+        <v>-0.8349</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1859</v>
+        <v>-0.8349</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1859</v>
+        <v>-0.8349</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1859</v>
+        <v>-0.8349</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1859</v>
+        <v>-0.8349</v>
       </c>
       <c r="N35" t="n">
         <v>79</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3333</v>
+        <v>-0.9664</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.5637</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9751</v>
+        <v>-1.0743</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3333</v>
+        <v>-0.9664</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3333</v>
+        <v>-0.9664</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3333</v>
+        <v>-0.9664</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3333</v>
+        <v>-0.9664</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3333</v>
+        <v>-0.9664</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>mizu</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4792</v>
+        <v>-1.0948</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.8628</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0332</v>
+        <v>-1.1323</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4792</v>
+        <v>-1.0948</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4792</v>
+        <v>-1.0948</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4792</v>
+        <v>-1.0948</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4792</v>
+        <v>-1.0948</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4792</v>
+        <v>-1.0948</v>
       </c>
       <c r="N37" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mizu</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.566</v>
+        <v>-1.318</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.9134</v>
+        <v>-0.7688</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0678</v>
+        <v>-1.233</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.566</v>
+        <v>-1.318</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.566</v>
+        <v>-1.318</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.566</v>
+        <v>-1.318</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.566</v>
+        <v>-1.318</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.566</v>
+        <v>-1.318</v>
       </c>
       <c r="N38" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8846</v>
+        <v>-1.4533</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.0993</v>
+        <v>-0.8477</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1947</v>
+        <v>-1.2941</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8846</v>
+        <v>-1.4533</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8846</v>
+        <v>-1.4533</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8846</v>
+        <v>-1.4533</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8846</v>
+        <v>-1.4533</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8846</v>
+        <v>-1.4533</v>
       </c>
       <c r="N39" t="n">
         <v>132</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1579</v>
+        <v>-1.8728</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.2587</v>
+        <v>-1.0924</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3036</v>
+        <v>-1.4835</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1579</v>
+        <v>-1.8728</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.1579</v>
+        <v>-1.8728</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.1579</v>
+        <v>-1.8728</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.1579</v>
+        <v>-1.8728</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.1579</v>
+        <v>-1.8728</v>
       </c>
       <c r="N40" t="n">
         <v>132</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.9151</v>
+        <v>-2.0515</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.7004</v>
+        <v>-1.1966</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6053</v>
+        <v>-1.5642</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.9151</v>
+        <v>-2.0515</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9151</v>
+        <v>-0.1206</v>
       </c>
       <c r="G41" t="n">
-        <v>-2</v>
+        <v>-1.9309</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9151</v>
+        <v>-0.1206</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7417</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-2</v>
+        <v>-1.9309</v>
       </c>
       <c r="K41" t="n">
         <v>177</v>
@@ -2323,7 +2323,7 @@
         <v>156</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.7417</v>
+        <v>-1.9936</v>
       </c>
       <c r="N41" t="n">
         <v>333</v>
@@ -2429,10 +2429,10 @@
         <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4278</v>
+        <v>0.374</v>
       </c>
       <c r="J2" t="n">
-        <v>10.695</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1064</v>
+        <v>0.065</v>
       </c>
       <c r="J3" t="n">
-        <v>2.66</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3303</v>
+        <v>-0.2088</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.2575</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3457</v>
+        <v>-0.2189</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.6425</v>
+        <v>-5.4725</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4759</v>
+        <v>-0.3071</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.8975</v>
+        <v>-7.6775</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5187</v>
+        <v>0.4404</v>
       </c>
       <c r="J7" t="n">
-        <v>12.9675</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.27</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4659</v>
+        <v>0.3913</v>
       </c>
       <c r="J8" t="n">
-        <v>11.6475</v>
+        <v>9.782500000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1737</v>
+        <v>0.1395</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3425</v>
+        <v>3.4875</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.32</v>
+        <v>-0.193</v>
       </c>
       <c r="J10" t="n">
-        <v>-8</v>
+        <v>-4.825</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.71</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5149</v>
+        <v>-0.3316</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.8725</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.08</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3506</v>
+        <v>0.2978</v>
       </c>
       <c r="J12" t="n">
-        <v>9.466200000000001</v>
+        <v>8.0406</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.03</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1788</v>
+        <v>0.136</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8276</v>
+        <v>3.672</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1381</v>
+        <v>0.099</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7287</v>
+        <v>2.673</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1803</v>
+        <v>-0.1592</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.8681</v>
+        <v>-4.2984</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6582</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.7714</v>
+        <v>-16.5888</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3795</v>
+        <v>0.426</v>
       </c>
       <c r="J17" t="n">
-        <v>10.2465</v>
+        <v>11.502</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.97</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0449</v>
+        <v>-0.0443</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2123</v>
+        <v>-1.1961</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.85</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2874</v>
+        <v>-0.1798</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.7598</v>
+        <v>-4.8546</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.85</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2874</v>
+        <v>-0.1798</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.7598</v>
+        <v>-4.8546</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3653</v>
+        <v>-0.2306</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.863099999999999</v>
+        <v>-6.2262</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4871</v>
+        <v>1.313</v>
       </c>
       <c r="J22" t="n">
-        <v>34.2033</v>
+        <v>30.199</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2426</v>
+        <v>0.2887</v>
       </c>
       <c r="J23" t="n">
-        <v>5.5798</v>
+        <v>6.6401</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0794</v>
+        <v>0.1351</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8262</v>
+        <v>3.1073</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0434</v>
+        <v>0.1005</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9982</v>
+        <v>2.3115</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.9</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4556</v>
+        <v>-0.387</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.4788</v>
+        <v>-8.901</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.07</v>
       </c>
       <c r="I27" t="n">
-        <v>0.266</v>
+        <v>0.2693</v>
       </c>
       <c r="J27" t="n">
-        <v>6.118</v>
+        <v>6.1939</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.92</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0725</v>
+        <v>-0.0819</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.6675</v>
+        <v>-1.8837</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.412</v>
+        <v>-0.2782</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.476000000000001</v>
+        <v>-6.3986</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4435</v>
+        <v>-0.2971</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.2005</v>
+        <v>-6.8333</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8144</v>
+        <v>-0.5581</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.7312</v>
+        <v>-12.8363</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.56</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.5372</v>
       </c>
       <c r="J32" t="n">
-        <v>15.9096</v>
+        <v>11.2812</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.3</v>
       </c>
       <c r="I33" t="n">
-        <v>0.439</v>
+        <v>0.369</v>
       </c>
       <c r="J33" t="n">
-        <v>9.218999999999999</v>
+        <v>7.749</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3798</v>
+        <v>0.341</v>
       </c>
       <c r="J34" t="n">
-        <v>7.9758</v>
+        <v>7.161</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.13</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1716</v>
+        <v>0.1882</v>
       </c>
       <c r="J35" t="n">
-        <v>3.6036</v>
+        <v>3.9522</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.98</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1373</v>
+        <v>-0.0601</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.8833</v>
+        <v>-1.2621</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5472</v>
+        <v>0.4339</v>
       </c>
       <c r="J37" t="n">
-        <v>11.4912</v>
+        <v>9.1119</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.71</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4369</v>
+        <v>-0.2952</v>
       </c>
       <c r="J38" t="n">
-        <v>-9.174899999999999</v>
+        <v>-6.1992</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.66</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5122</v>
+        <v>-0.3422</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.7562</v>
+        <v>-7.1862</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.596</v>
+        <v>-0.3985</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.516</v>
+        <v>-8.368499999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6361</v>
+        <v>-0.4265</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.3581</v>
+        <v>-8.9565</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.72</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.3488</v>
+        <v>-0.2739</v>
       </c>
       <c r="J42" t="n">
-        <v>-7.6736</v>
+        <v>-6.0258</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.71</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3652</v>
+        <v>-0.2836</v>
       </c>
       <c r="J43" t="n">
-        <v>-8.0344</v>
+        <v>-6.2392</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.66</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4619</v>
+        <v>-0.329</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.1618</v>
+        <v>-7.238</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.64</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4983</v>
+        <v>-0.3469</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.9626</v>
+        <v>-7.6318</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5615</v>
+        <v>-0.3836</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.353</v>
+        <v>-8.4392</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.64</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4651</v>
+        <v>1.0285</v>
       </c>
       <c r="J47" t="n">
-        <v>32.2322</v>
+        <v>22.627</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.37</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9194</v>
+        <v>0.6882</v>
       </c>
       <c r="J48" t="n">
-        <v>20.2268</v>
+        <v>15.1404</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.23</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5569</v>
+        <v>0.5037</v>
       </c>
       <c r="J49" t="n">
-        <v>12.2518</v>
+        <v>11.0814</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.21</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5041</v>
+        <v>0.4757</v>
       </c>
       <c r="J50" t="n">
-        <v>11.0902</v>
+        <v>10.4654</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6473</v>
+        <v>-0.5837</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.2406</v>
+        <v>-12.8414</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.9</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1383</v>
+        <v>-0.1172</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.2554</v>
+        <v>-4.4536</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.89</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1564</v>
+        <v>-0.1283</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.9432</v>
+        <v>-4.8754</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.86</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2109</v>
+        <v>-0.1603</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.014200000000001</v>
+        <v>-6.0914</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.275</v>
+        <v>-0.1898</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.45</v>
+        <v>-7.2124</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4817</v>
+        <v>-0.3156</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.3046</v>
+        <v>-11.9928</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9339</v>
+        <v>0.6782</v>
       </c>
       <c r="J57" t="n">
-        <v>35.4882</v>
+        <v>25.7716</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6774</v>
+        <v>0.5231</v>
       </c>
       <c r="J58" t="n">
-        <v>25.7412</v>
+        <v>19.8778</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2982</v>
+        <v>0.3207</v>
       </c>
       <c r="J59" t="n">
-        <v>11.3316</v>
+        <v>12.1866</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1434</v>
+        <v>-0.0798</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.4492</v>
+        <v>-3.0324</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5009</v>
+        <v>-0.4365</v>
       </c>
       <c r="J61" t="n">
-        <v>-19.0342</v>
+        <v>-16.587</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1876</v>
+        <v>0.1345</v>
       </c>
       <c r="J62" t="n">
-        <v>5.0652</v>
+        <v>3.6315</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0046</v>
+        <v>-0.0217</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1242</v>
+        <v>-0.5859</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.119</v>
+        <v>-0.0994</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.213</v>
+        <v>-2.6838</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3766</v>
+        <v>-0.2431</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.1682</v>
+        <v>-6.5637</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.63</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5856</v>
+        <v>-0.3866</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.8112</v>
+        <v>-10.4382</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6786</v>
+        <v>0.4878</v>
       </c>
       <c r="J67" t="n">
-        <v>18.3222</v>
+        <v>13.1706</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0843</v>
+        <v>0.0906</v>
       </c>
       <c r="J68" t="n">
-        <v>2.2761</v>
+        <v>2.4462</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0409</v>
+        <v>-0.0072</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.1043</v>
+        <v>-0.1944</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0283</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.0358</v>
+        <v>-0.7641</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.93</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1995</v>
+        <v>-0.109</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.3865</v>
+        <v>-2.943</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0919</v>
+        <v>0.7752</v>
       </c>
       <c r="J72" t="n">
-        <v>28.3894</v>
+        <v>20.1552</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7803</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>20.2878</v>
+        <v>15.0306</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.21</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.5046</v>
       </c>
       <c r="J74" t="n">
-        <v>17.1288</v>
+        <v>13.1196</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.84</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5876</v>
+        <v>-0.5319</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.2776</v>
+        <v>-13.8294</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1987</v>
+        <v>-1.2003</v>
       </c>
       <c r="J76" t="n">
-        <v>-31.1662</v>
+        <v>-31.2078</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3669</v>
+        <v>0.3783</v>
       </c>
       <c r="J77" t="n">
-        <v>9.539400000000001</v>
+        <v>9.835800000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.03</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1258</v>
+        <v>0.1093</v>
       </c>
       <c r="J78" t="n">
-        <v>3.2708</v>
+        <v>2.8418</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0533</v>
       </c>
       <c r="J79" t="n">
-        <v>2.0202</v>
+        <v>1.3858</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.73</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4641</v>
+        <v>-0.2985</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.0666</v>
+        <v>-7.761</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.68</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5315</v>
+        <v>-0.3462</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.819</v>
+        <v>-9.001200000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.8</v>
       </c>
       <c r="I82" t="n">
-        <v>1.7542</v>
+        <v>1.242</v>
       </c>
       <c r="J82" t="n">
-        <v>43.855</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7454</v>
+        <v>0.5778</v>
       </c>
       <c r="J83" t="n">
-        <v>18.635</v>
+        <v>14.445</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.01</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.064</v>
+        <v>0.0068</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.6</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.96</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.295</v>
+        <v>-0.2165</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.375</v>
+        <v>-5.4125</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3593</v>
+        <v>-0.2822</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.9825</v>
+        <v>-7.055</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.5853</v>
       </c>
       <c r="J87" t="n">
-        <v>15.5375</v>
+        <v>14.6325</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.73</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.425</v>
+        <v>-0.282</v>
       </c>
       <c r="J88" t="n">
-        <v>-10.625</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.68</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4985</v>
+        <v>-0.3295</v>
       </c>
       <c r="J89" t="n">
-        <v>-12.4625</v>
+        <v>-8.237500000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5541</v>
+        <v>-0.3672</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.8525</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5677</v>
+        <v>-0.3766</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.1925</v>
+        <v>-9.414999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.42</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7171</v>
+        <v>0.8927</v>
       </c>
       <c r="J92" t="n">
-        <v>18.6446</v>
+        <v>23.2102</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.92</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.118</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.068</v>
+        <v>-2.5766</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.91</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.137</v>
+        <v>-0.1106</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.562</v>
+        <v>-2.8756</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.6737</v>
+        <v>-0.4512</v>
       </c>
       <c r="J95" t="n">
-        <v>-17.5162</v>
+        <v>-11.7312</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.54</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6983</v>
+        <v>-0.4696</v>
       </c>
       <c r="J96" t="n">
-        <v>-18.1558</v>
+        <v>-12.2096</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3816</v>
+        <v>1.243</v>
       </c>
       <c r="J97" t="n">
-        <v>35.9216</v>
+        <v>32.318</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.44</v>
       </c>
       <c r="I98" t="n">
-        <v>1.1223</v>
+        <v>1.0745</v>
       </c>
       <c r="J98" t="n">
-        <v>29.1798</v>
+        <v>27.937</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2071</v>
+        <v>-0.1335</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.3846</v>
+        <v>-3.471</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3131</v>
+        <v>-0.2391</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.140599999999999</v>
+        <v>-6.2166</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.84</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6207</v>
+        <v>-0.5591</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.1382</v>
+        <v>-14.5366</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3991</v>
+        <v>0.3299</v>
       </c>
       <c r="J102" t="n">
-        <v>15.964</v>
+        <v>13.196</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.13</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2633</v>
+        <v>0.2113</v>
       </c>
       <c r="J103" t="n">
-        <v>10.532</v>
+        <v>8.452</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.96</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1291</v>
+        <v>-0.067</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.164</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1684</v>
+        <v>-0.0921</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.736</v>
+        <v>-3.684</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1684</v>
+        <v>-0.0921</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.736</v>
+        <v>-3.684</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4944</v>
+        <v>0.4439</v>
       </c>
       <c r="J107" t="n">
-        <v>19.776</v>
+        <v>17.756</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2432</v>
+        <v>0.1969</v>
       </c>
       <c r="J108" t="n">
-        <v>9.728</v>
+        <v>7.876</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3287</v>
+        <v>-0.2039</v>
       </c>
       <c r="J109" t="n">
-        <v>-13.148</v>
+        <v>-8.156000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3439</v>
+        <v>-0.2141</v>
       </c>
       <c r="J110" t="n">
-        <v>-13.756</v>
+        <v>-8.564</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4027</v>
+        <v>-0.2542</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.108</v>
+        <v>-10.168</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.02</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1698</v>
+        <v>0.1453</v>
       </c>
       <c r="J112" t="n">
-        <v>3.7356</v>
+        <v>3.1966</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0318</v>
+        <v>-0.0549</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.6996</v>
+        <v>-1.2078</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2403</v>
+        <v>-0.1915</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.2866</v>
+        <v>-4.213</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6377</v>
+        <v>-0.4274</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.0294</v>
+        <v>-9.402799999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.47</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7645</v>
+        <v>-0.5202</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.819</v>
+        <v>-11.4444</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.5</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1793</v>
+        <v>1.1223</v>
       </c>
       <c r="J117" t="n">
-        <v>25.9446</v>
+        <v>24.6906</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.42</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0128</v>
+        <v>1.0172</v>
       </c>
       <c r="J118" t="n">
-        <v>22.2816</v>
+        <v>22.3784</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.3</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7325</v>
+        <v>0.7743</v>
       </c>
       <c r="J119" t="n">
-        <v>16.115</v>
+        <v>17.0346</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2809</v>
+        <v>0.3647</v>
       </c>
       <c r="J120" t="n">
-        <v>6.1798</v>
+        <v>8.023400000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.09</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1708</v>
+        <v>0.2532</v>
       </c>
       <c r="J121" t="n">
-        <v>3.7576</v>
+        <v>5.5704</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.71</v>
       </c>
       <c r="I122" t="n">
-        <v>1.6064</v>
+        <v>1.3951</v>
       </c>
       <c r="J122" t="n">
-        <v>35.3408</v>
+        <v>30.6922</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.3</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7853</v>
       </c>
       <c r="J123" t="n">
-        <v>16.9994</v>
+        <v>17.2766</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3867</v>
+        <v>0.456</v>
       </c>
       <c r="J124" t="n">
-        <v>8.507400000000001</v>
+        <v>10.032</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0346</v>
+        <v>0.0394</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.7612</v>
+        <v>0.8668</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.97</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2716</v>
+        <v>-0.19</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.9752</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2934</v>
+        <v>0.3057</v>
       </c>
       <c r="J127" t="n">
-        <v>6.4548</v>
+        <v>6.7254</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.79</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.283</v>
+        <v>-0.2195</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.226</v>
+        <v>-4.829</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.68</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4795</v>
+        <v>-0.3222</v>
       </c>
       <c r="J129" t="n">
-        <v>-10.549</v>
+        <v>-7.0884</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.66</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5092</v>
+        <v>-0.341</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.2024</v>
+        <v>-7.502</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.54</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6732</v>
+        <v>-0.4533</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.8104</v>
+        <v>-9.9726</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1732</v>
+        <v>1.1038</v>
       </c>
       <c r="J132" t="n">
-        <v>28.1568</v>
+        <v>26.4912</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.41</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0901</v>
+        <v>1.0495</v>
       </c>
       <c r="J133" t="n">
-        <v>26.1624</v>
+        <v>25.188</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4445</v>
+        <v>0.4298</v>
       </c>
       <c r="J134" t="n">
-        <v>10.668</v>
+        <v>10.3152</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.322</v>
+        <v>-0.2559</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.728</v>
+        <v>-6.1416</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.55</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.2472</v>
+        <v>-1.2562</v>
       </c>
       <c r="J136" t="n">
-        <v>-29.9328</v>
+        <v>-30.1488</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.418</v>
+        <v>0.475</v>
       </c>
       <c r="J137" t="n">
-        <v>10.032</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2123</v>
+        <v>0.2106</v>
       </c>
       <c r="J138" t="n">
-        <v>5.0952</v>
+        <v>5.0544</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.78</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3872</v>
+        <v>-0.2472</v>
       </c>
       <c r="J139" t="n">
-        <v>-9.2928</v>
+        <v>-5.9328</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.445</v>
+        <v>-0.2863</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.68</v>
+        <v>-6.8712</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.459</v>
+        <v>-0.2959</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.016</v>
+        <v>-7.1016</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.513</v>
+        <v>0.6107</v>
       </c>
       <c r="J142" t="n">
-        <v>11.286</v>
+        <v>13.4354</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.88</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1287</v>
+        <v>-0.1223</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.8314</v>
+        <v>-2.6906</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.79</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2784</v>
+        <v>-0.2183</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.1248</v>
+        <v>-4.8026</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.49</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.735</v>
+        <v>-0.4986</v>
       </c>
       <c r="J145" t="n">
-        <v>-16.17</v>
+        <v>-10.9692</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.33</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.9273</v>
+        <v>-0.6463</v>
       </c>
       <c r="J146" t="n">
-        <v>-20.4006</v>
+        <v>-14.2186</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.49</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2021</v>
+        <v>1.1286</v>
       </c>
       <c r="J147" t="n">
-        <v>26.4462</v>
+        <v>24.8292</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.31</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8153</v>
+        <v>0.8165</v>
       </c>
       <c r="J148" t="n">
-        <v>17.9366</v>
+        <v>17.963</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.695</v>
+        <v>0.7008</v>
       </c>
       <c r="J149" t="n">
-        <v>15.29</v>
+        <v>15.4176</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.15</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3779</v>
+        <v>0.4371</v>
       </c>
       <c r="J150" t="n">
-        <v>8.313800000000001</v>
+        <v>9.616199999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7534</v>
+        <v>-0.7008</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.5748</v>
+        <v>-15.4176</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.13</v>
       </c>
       <c r="I152" t="n">
-        <v>1.335</v>
+        <v>1.1581</v>
       </c>
       <c r="J152" t="n">
-        <v>32.04</v>
+        <v>27.7944</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4592</v>
+        <v>0.4068</v>
       </c>
       <c r="J153" t="n">
-        <v>11.0208</v>
+        <v>9.763199999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.239</v>
+        <v>0.2425</v>
       </c>
       <c r="J154" t="n">
-        <v>5.736</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.84</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3679</v>
+        <v>-0.2219</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.829599999999999</v>
+        <v>-5.3256</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5645</v>
+        <v>-0.3674</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.548</v>
+        <v>-8.817600000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.98</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0379</v>
+        <v>-0.0061</v>
       </c>
       <c r="J157" t="n">
-        <v>0.9096</v>
+        <v>-0.1464</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.85</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2052</v>
+        <v>-0.1651</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.9248</v>
+        <v>-3.9624</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.82</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2575</v>
+        <v>-0.1958</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.18</v>
+        <v>-4.6992</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.32</v>
+        <v>-0.2243</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.68</v>
+        <v>-5.3832</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.4689</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.7064</v>
+        <v>-11.2536</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2561</v>
+        <v>0.268</v>
       </c>
       <c r="J162" t="n">
-        <v>6.9147</v>
+        <v>7.236</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2391</v>
+        <v>0.2469</v>
       </c>
       <c r="J163" t="n">
-        <v>6.4557</v>
+        <v>6.6663</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0572</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.7604</v>
+        <v>-1.5444</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.235</v>
+        <v>-0.1478</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.345</v>
+        <v>-3.9906</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6342</v>
+        <v>-0.4211</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.1234</v>
+        <v>-11.3697</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.8996</v>
       </c>
       <c r="J167" t="n">
-        <v>24.9723</v>
+        <v>24.2892</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.4986</v>
       </c>
       <c r="J168" t="n">
-        <v>14.4936</v>
+        <v>13.4622</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4253</v>
+        <v>0.3908</v>
       </c>
       <c r="J169" t="n">
-        <v>11.4831</v>
+        <v>10.5516</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6088</v>
+        <v>-0.5552</v>
       </c>
       <c r="J170" t="n">
-        <v>-16.4376</v>
+        <v>-14.9904</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7086</v>
+        <v>-0.6601</v>
       </c>
       <c r="J171" t="n">
-        <v>-19.1322</v>
+        <v>-17.8227</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.08</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3109</v>
+        <v>0.331</v>
       </c>
       <c r="J172" t="n">
-        <v>7.4616</v>
+        <v>7.944</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.76</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3108</v>
+        <v>-0.2431</v>
       </c>
       <c r="J173" t="n">
-        <v>-7.4592</v>
+        <v>-5.8344</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3445</v>
+        <v>-0.2624</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.268000000000001</v>
+        <v>-6.2976</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5808</v>
+        <v>-0.3912</v>
       </c>
       <c r="J175" t="n">
-        <v>-13.9392</v>
+        <v>-9.3888</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.38</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.864</v>
+        <v>-0.5964</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.736</v>
+        <v>-14.3136</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3617</v>
+        <v>1.2336</v>
       </c>
       <c r="J177" t="n">
-        <v>32.6808</v>
+        <v>29.6064</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1025</v>
+        <v>1.0693</v>
       </c>
       <c r="J178" t="n">
-        <v>26.46</v>
+        <v>25.6632</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2758</v>
+        <v>0.3496</v>
       </c>
       <c r="J179" t="n">
-        <v>6.6192</v>
+        <v>8.3904</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1009</v>
+        <v>0.1754</v>
       </c>
       <c r="J180" t="n">
-        <v>2.4216</v>
+        <v>4.2096</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.97</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2728</v>
+        <v>-0.191</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.5472</v>
+        <v>-4.584</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.89</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1388</v>
+        <v>-0.1226</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.7476</v>
+        <v>-3.3102</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.88</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1563</v>
+        <v>-0.1338</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.2201</v>
+        <v>-3.6126</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3028</v>
+        <v>-0.2156</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.175599999999999</v>
+        <v>-5.8212</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.77</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.361</v>
+        <v>-0.2438</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.747</v>
+        <v>-6.5826</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.66</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5266</v>
+        <v>-0.3484</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.2182</v>
+        <v>-9.4068</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.48</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1949</v>
+        <v>1.1222</v>
       </c>
       <c r="J187" t="n">
-        <v>32.2623</v>
+        <v>30.2994</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.24</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6616</v>
+        <v>0.6601</v>
       </c>
       <c r="J188" t="n">
-        <v>17.8632</v>
+        <v>17.8227</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3085</v>
+        <v>0.3636</v>
       </c>
       <c r="J189" t="n">
-        <v>8.329499999999999</v>
+        <v>9.8172</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.02</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0122</v>
+        <v>0.0539</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.3294</v>
+        <v>1.4553</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0545</v>
+        <v>0.0129</v>
       </c>
       <c r="J191" t="n">
-        <v>-1.4715</v>
+        <v>0.3483</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4716</v>
+        <v>0.5558</v>
       </c>
       <c r="J192" t="n">
-        <v>9.432</v>
+        <v>11.116</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.74</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3419</v>
+        <v>-0.2618</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.838</v>
+        <v>-5.236</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.59</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.5934</v>
+        <v>-0.3999</v>
       </c>
       <c r="J194" t="n">
-        <v>-11.868</v>
+        <v>-7.998</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.54</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6616</v>
+        <v>-0.4466</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.232</v>
+        <v>-8.932</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.49</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.727</v>
+        <v>-0.4934</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.54</v>
+        <v>-9.868</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>1.5641</v>
+        <v>1.3686</v>
       </c>
       <c r="J197" t="n">
-        <v>31.282</v>
+        <v>27.372</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.3</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7361</v>
+        <v>0.7749</v>
       </c>
       <c r="J198" t="n">
-        <v>14.722</v>
+        <v>15.498</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4893</v>
+        <v>0.5693</v>
       </c>
       <c r="J199" t="n">
-        <v>9.786</v>
+        <v>11.386</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.15</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3353</v>
+        <v>0.4186</v>
       </c>
       <c r="J200" t="n">
-        <v>6.706</v>
+        <v>8.372</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.06</v>
       </c>
       <c r="I201" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.1639</v>
       </c>
       <c r="J201" t="n">
-        <v>1.672</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.52</v>
       </c>
       <c r="I202" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J202" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>2.24</v>
       </c>
       <c r="I203" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J203" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.71</v>
       </c>
       <c r="I204" t="n">
-        <v>1.3956</v>
+        <v>1.3142</v>
       </c>
       <c r="J204" t="n">
-        <v>22.3296</v>
+        <v>21.0272</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.28</v>
       </c>
       <c r="I205" t="n">
-        <v>0.518</v>
+        <v>0.6536</v>
       </c>
       <c r="J205" t="n">
-        <v>8.288</v>
+        <v>10.4576</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.72</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.9809</v>
+        <v>-0.9579</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.6944</v>
+        <v>-15.3264</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.4</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.6072</v>
+        <v>-0.4872</v>
       </c>
       <c r="J207" t="n">
-        <v>-9.715199999999999</v>
+        <v>-7.7952</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.35</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.6997</v>
+        <v>-0.542</v>
       </c>
       <c r="J208" t="n">
-        <v>-11.1952</v>
+        <v>-8.672000000000001</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.35</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.6997</v>
+        <v>-0.542</v>
       </c>
       <c r="J209" t="n">
-        <v>-11.1952</v>
+        <v>-8.672000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.31</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-0.5798</v>
       </c>
       <c r="J210" t="n">
-        <v>-12.8464</v>
+        <v>-9.2768</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.21</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.6889</v>
       </c>
       <c r="J211" t="n">
-        <v>-15.7024</v>
+        <v>-11.0224</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1825</v>
+        <v>0.162</v>
       </c>
       <c r="J212" t="n">
-        <v>4.38</v>
+        <v>3.888</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.8</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2886</v>
+        <v>-0.2144</v>
       </c>
       <c r="J213" t="n">
-        <v>-6.9264</v>
+        <v>-5.1456</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3333</v>
+        <v>-0.2329</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.9992</v>
+        <v>-5.5896</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4792</v>
+        <v>-0.318</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.5008</v>
+        <v>-7.632</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5636</v>
+        <v>-0.3746</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.5264</v>
+        <v>-8.990399999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3133</v>
+        <v>1.1989</v>
       </c>
       <c r="J217" t="n">
-        <v>31.5192</v>
+        <v>28.7736</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.32</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8518</v>
+        <v>0.8468</v>
       </c>
       <c r="J218" t="n">
-        <v>20.4432</v>
+        <v>20.3232</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8057</v>
+        <v>0.8005</v>
       </c>
       <c r="J219" t="n">
-        <v>19.3368</v>
+        <v>19.212</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4963</v>
+        <v>-0.4262</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.9112</v>
+        <v>-10.2288</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.83</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6512</v>
+        <v>-0.5908</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.6288</v>
+        <v>-14.1792</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.48</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7503</v>
+        <v>0.9332</v>
       </c>
       <c r="J222" t="n">
-        <v>21.7587</v>
+        <v>27.0628</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.379</v>
+        <v>0.4295</v>
       </c>
       <c r="J223" t="n">
-        <v>10.991</v>
+        <v>12.4555</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.79</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3913</v>
+        <v>-0.2457</v>
       </c>
       <c r="J224" t="n">
-        <v>-11.3477</v>
+        <v>-7.1253</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.74</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4614</v>
+        <v>-0.2947</v>
       </c>
       <c r="J225" t="n">
-        <v>-13.3806</v>
+        <v>-8.5463</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5668</v>
+        <v>-0.3707</v>
       </c>
       <c r="J226" t="n">
-        <v>-16.4372</v>
+        <v>-10.7503</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7307</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J227" t="n">
-        <v>21.1903</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.07</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2899</v>
+        <v>0.2546</v>
       </c>
       <c r="J228" t="n">
-        <v>8.4071</v>
+        <v>7.3834</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.99</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0878</v>
+        <v>-0.0571</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.5462</v>
+        <v>-1.6559</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2815</v>
+        <v>-0.2339</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.163500000000001</v>
+        <v>-6.7831</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5189</v>
+        <v>-0.4665</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.0481</v>
+        <v>-13.5285</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.62</v>
       </c>
       <c r="I232" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J232" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.68</v>
       </c>
       <c r="I233" t="n">
-        <v>1.4142</v>
+        <v>1.2962</v>
       </c>
       <c r="J233" t="n">
-        <v>22.6272</v>
+        <v>20.7392</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.51</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0456</v>
+        <v>1.1028</v>
       </c>
       <c r="J234" t="n">
-        <v>16.7296</v>
+        <v>17.6448</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.01</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1541</v>
+        <v>-0.068</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.4656</v>
+        <v>-1.088</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.89</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5754</v>
+        <v>-0.5029</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.2064</v>
+        <v>-8.0464</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.79</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1431</v>
+        <v>-0.1385</v>
       </c>
       <c r="J237" t="n">
-        <v>-2.2896</v>
+        <v>-2.216</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3274</v>
+        <v>-0.2773</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.2384</v>
+        <v>-4.4368</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.4</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.7805</v>
+        <v>-0.5401</v>
       </c>
       <c r="J239" t="n">
-        <v>-12.488</v>
+        <v>-8.6416</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.35</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.8512</v>
+        <v>-0.5893</v>
       </c>
       <c r="J240" t="n">
-        <v>-13.6192</v>
+        <v>-9.428800000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.31</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.9055</v>
+        <v>-0.6291</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.488</v>
+        <v>-10.0656</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.52</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2709</v>
+        <v>1.1717</v>
       </c>
       <c r="J242" t="n">
-        <v>35.5852</v>
+        <v>32.8076</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8023</v>
+        <v>0.7987</v>
       </c>
       <c r="J243" t="n">
-        <v>22.4644</v>
+        <v>22.3636</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3612</v>
+        <v>0.4149</v>
       </c>
       <c r="J244" t="n">
-        <v>10.1136</v>
+        <v>11.6172</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1165</v>
+        <v>-0.0441</v>
       </c>
       <c r="J245" t="n">
-        <v>-3.262</v>
+        <v>-1.2348</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.95</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3224</v>
+        <v>-0.2459</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.027200000000001</v>
+        <v>-6.8852</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.2</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4616</v>
+        <v>0.5337</v>
       </c>
       <c r="J247" t="n">
-        <v>12.9248</v>
+        <v>14.9436</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.83</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2398</v>
+        <v>-0.1857</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.7144</v>
+        <v>-5.1996</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.66</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.3475</v>
       </c>
       <c r="J249" t="n">
-        <v>-14.6916</v>
+        <v>-9.73</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.65</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5386</v>
+        <v>-0.3569</v>
       </c>
       <c r="J250" t="n">
-        <v>-15.0808</v>
+        <v>-9.9932</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.63</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.3758</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.848</v>
+        <v>-10.5224</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1615/event_1615_evp_summary.xlsx
+++ b/database/event/1615/event_1615_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8236</v>
+        <v>6.1431</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3969</v>
+        <v>3.5833</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9911</v>
+        <v>2.1723</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8236</v>
+        <v>6.1431</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7138</v>
+        <v>2.8068</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1097</v>
+        <v>3.3363</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0756</v>
+        <v>4.3664</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1191</v>
+        <v>2.3578</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1097</v>
+        <v>3.3363</v>
       </c>
       <c r="K2" t="n">
         <v>36</v>
@@ -529,7 +529,7 @@
         <v>153</v>
       </c>
       <c r="M2" t="n">
-        <v>5.2288</v>
+        <v>5.694100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>189</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7083</v>
+        <v>3.7417</v>
       </c>
       <c r="C3" t="n">
-        <v>2.163</v>
+        <v>2.1825</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0361</v>
+        <v>1.0791</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7083</v>
+        <v>3.7417</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0215</v>
+        <v>2.9734</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6868</v>
+        <v>0.7683</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1597</v>
+        <v>4.916</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6828</v>
+        <v>2.6546</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6868</v>
+        <v>0.7683</v>
       </c>
       <c r="K3" t="n">
         <v>36</v>
@@ -575,7 +575,7 @@
         <v>153</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3696</v>
+        <v>3.4229</v>
       </c>
       <c r="N3" t="n">
         <v>189</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6755</v>
+        <v>3.5914</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1439</v>
+        <v>2.0949</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0213</v>
+        <v>1.0107</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6755</v>
+        <v>3.5914</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6122</v>
+        <v>2.5001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0633</v>
+        <v>1.0913</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7174</v>
+        <v>3.3547</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9329</v>
+        <v>1.8115</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0633</v>
+        <v>1.0913</v>
       </c>
       <c r="K4" t="n">
         <v>177</v>
@@ -621,7 +621,7 @@
         <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9962</v>
+        <v>2.9028</v>
       </c>
       <c r="N4" t="n">
         <v>333</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5164</v>
+        <v>3.4829</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0511</v>
+        <v>2.0316</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9495</v>
+        <v>0.9613</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5164</v>
+        <v>3.4829</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9868</v>
+        <v>2.908</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5296</v>
+        <v>0.5749</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0372</v>
+        <v>4.7003</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6191</v>
+        <v>2.5381</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5296</v>
+        <v>0.5749</v>
       </c>
       <c r="K5" t="n">
         <v>103</v>
@@ -667,7 +667,7 @@
         <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1487</v>
+        <v>3.113</v>
       </c>
       <c r="N5" t="n">
         <v>181</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.007</v>
+        <v>2.9558</v>
       </c>
       <c r="C6" t="n">
-        <v>1.754</v>
+        <v>1.7241</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7195</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.007</v>
+        <v>2.9558</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6727</v>
+        <v>2.5541</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3343</v>
+        <v>0.4017</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9307</v>
+        <v>3.5326</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0438</v>
+        <v>1.9076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3343</v>
+        <v>0.4017</v>
       </c>
       <c r="K6" t="n">
         <v>177</v>
@@ -713,7 +713,7 @@
         <v>156</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3781</v>
+        <v>2.3093</v>
       </c>
       <c r="N6" t="n">
         <v>333</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.521</v>
+        <v>2.4494</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4705</v>
+        <v>1.4287</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5001</v>
+        <v>0.4908</v>
       </c>
       <c r="E7" t="n">
-        <v>2.521</v>
+        <v>2.4494</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6413</v>
+        <v>2.5678</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1203</v>
+        <v>-0.1184</v>
       </c>
       <c r="H7" t="n">
-        <v>3.82</v>
+        <v>3.5778</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9862</v>
+        <v>1.932</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1203</v>
+        <v>-0.1184</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8659</v>
+        <v>1.8136</v>
       </c>
       <c r="N7" t="n">
         <v>126</v>
@@ -768,170 +768,170 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2184</v>
+        <v>2.2925</v>
       </c>
       <c r="C8" t="n">
-        <v>1.294</v>
+        <v>1.3372</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3635</v>
+        <v>0.4194</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2184</v>
+        <v>2.2925</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4534</v>
+        <v>2.9662</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.235</v>
+        <v>-0.6737</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1578</v>
+        <v>4.8923</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6419</v>
+        <v>2.6418</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.235</v>
+        <v>-0.6737</v>
       </c>
       <c r="K8" t="n">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4069</v>
+        <v>1.9681</v>
       </c>
       <c r="N8" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2016</v>
+        <v>2.1583</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2842</v>
+        <v>1.2589</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3559</v>
+        <v>0.3583</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2016</v>
+        <v>2.1583</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9083</v>
+        <v>2.3548</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7067</v>
+        <v>-0.1965</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7609</v>
+        <v>2.8752</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4754</v>
+        <v>1.5526</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7067</v>
+        <v>-0.1965</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="L9" t="n">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7687</v>
+        <v>1.3561</v>
       </c>
       <c r="N9" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7088</v>
+        <v>1.6212</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9967</v>
+        <v>0.9456</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1334</v>
+        <v>0.1138</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7088</v>
+        <v>1.6212</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7088</v>
+        <v>2.3191</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.6979</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7088</v>
+        <v>2.7575</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7088</v>
+        <v>1.489</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.6979</v>
       </c>
       <c r="K10" t="n">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7088</v>
+        <v>0.7911000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5878</v>
+        <v>1.5927</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9262</v>
+        <v>0.929</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0788</v>
+        <v>0.1008</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5878</v>
+        <v>1.5927</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5878</v>
+        <v>1.5927</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5878</v>
+        <v>1.5927</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5878</v>
+        <v>1.5927</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5878</v>
+        <v>1.5927</v>
       </c>
       <c r="N11" t="n">
         <v>132</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5714</v>
+        <v>1.4611</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9166</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0409</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5714</v>
+        <v>1.4611</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2307</v>
+        <v>1.4611</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6593</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3733</v>
+        <v>1.4611</v>
       </c>
       <c r="I12" t="n">
-        <v>1.234</v>
+        <v>1.4611</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6593</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5747</v>
+        <v>1.4611</v>
       </c>
       <c r="N12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4264</v>
+        <v>1.3882</v>
       </c>
       <c r="C13" t="n">
-        <v>0.832</v>
+        <v>0.8097</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0059</v>
+        <v>0.0077</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4264</v>
+        <v>1.3882</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4264</v>
+        <v>1.3882</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4264</v>
+        <v>1.3882</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4264</v>
+        <v>1.3882</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4264</v>
+        <v>1.3882</v>
       </c>
       <c r="N13" t="n">
         <v>97</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4219</v>
+        <v>1.2614</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8294</v>
+        <v>0.7358</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0039</v>
+        <v>-0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4219</v>
+        <v>1.2614</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0948</v>
+        <v>1.5539</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.2925</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0948</v>
+        <v>1.5539</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0892</v>
+        <v>0.8391</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.2925</v>
       </c>
       <c r="K14" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="L14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4162999999999999</v>
+        <v>0.5466</v>
       </c>
       <c r="N14" t="n">
-        <v>181</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3952</v>
+        <v>1.2494</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8138</v>
+        <v>0.7288</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0555</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3952</v>
+        <v>1.2494</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6711</v>
+        <v>1.9497</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2759</v>
+        <v>-0.7003</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6711</v>
+        <v>1.9497</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8689</v>
+        <v>1.0528</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2759</v>
+        <v>-0.7003</v>
       </c>
       <c r="K15" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="L15" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>0.593</v>
+        <v>0.3524999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>126</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.24</v>
+        <v>1.1352</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6622</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.1074</v>
       </c>
       <c r="E16" t="n">
-        <v>1.24</v>
+        <v>1.1352</v>
       </c>
       <c r="F16" t="n">
-        <v>0.47</v>
+        <v>0.2765</v>
       </c>
       <c r="G16" t="n">
-        <v>0.77</v>
+        <v>0.8587</v>
       </c>
       <c r="H16" t="n">
-        <v>0.47</v>
+        <v>0.2765</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2444</v>
+        <v>0.1493</v>
       </c>
       <c r="J16" t="n">
-        <v>0.77</v>
+        <v>0.8587</v>
       </c>
       <c r="K16" t="n">
         <v>177</v>
@@ -1173,7 +1173,7 @@
         <v>156</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0144</v>
+        <v>1.008</v>
       </c>
       <c r="N16" t="n">
         <v>333</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2113</v>
+        <v>1.1023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7066</v>
+        <v>0.643</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0912</v>
+        <v>-0.1224</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2113</v>
+        <v>1.1023</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2113</v>
+        <v>1.1023</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2113</v>
+        <v>1.1023</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2113</v>
+        <v>1.1023</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2113</v>
+        <v>1.1023</v>
       </c>
       <c r="N17" t="n">
         <v>113</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0894</v>
+        <v>1.0509</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6354</v>
+        <v>0.613</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1462</v>
+        <v>-0.1458</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0894</v>
+        <v>1.0509</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0894</v>
+        <v>1.0509</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0894</v>
+        <v>1.0509</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0894</v>
+        <v>1.0509</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0894</v>
+        <v>1.0509</v>
       </c>
       <c r="N18" t="n">
         <v>97</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0215</v>
+        <v>0.8966</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5958</v>
+        <v>0.523</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1769</v>
+        <v>-0.2161</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0215</v>
+        <v>0.8966</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1511</v>
+        <v>1.0263</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1296</v>
+        <v>-0.1297</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1511</v>
+        <v>1.0263</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5985</v>
+        <v>0.5542</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1296</v>
+        <v>-0.1297</v>
       </c>
       <c r="K19" t="n">
         <v>103</v>
@@ -1311,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4689</v>
+        <v>0.4245</v>
       </c>
       <c r="N19" t="n">
         <v>181</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8929</v>
+        <v>0.8951</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5208</v>
+        <v>0.5221</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2349</v>
+        <v>-0.2167</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8929</v>
+        <v>0.8951</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8929</v>
+        <v>-0.4482</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.3432</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8929</v>
+        <v>-0.4482</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8929</v>
+        <v>-0.242</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.3432</v>
       </c>
       <c r="K20" t="n">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8929</v>
+        <v>1.1012</v>
       </c>
       <c r="N20" t="n">
-        <v>113</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7906</v>
+        <v>0.8086</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4612</v>
+        <v>0.4717</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2811</v>
+        <v>-0.2561</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7906</v>
+        <v>0.8086</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4164</v>
+        <v>0.8086</v>
       </c>
       <c r="G21" t="n">
-        <v>1.207</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4164</v>
+        <v>0.8086</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2165</v>
+        <v>0.8086</v>
       </c>
       <c r="J21" t="n">
-        <v>1.207</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="L21" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9905</v>
+        <v>0.8086</v>
       </c>
       <c r="N21" t="n">
-        <v>333</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>0.5728</v>
       </c>
       <c r="C22" t="n">
-        <v>0.35</v>
+        <v>0.3341</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3671</v>
+        <v>-0.3635</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6</v>
+        <v>0.5728</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5723</v>
+        <v>1.5426</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9698</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5723</v>
+        <v>1.5426</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8175</v>
+        <v>0.833</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9698</v>
       </c>
       <c r="K22" t="n">
         <v>36</v>
@@ -1449,7 +1449,7 @@
         <v>153</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1548</v>
+        <v>-0.1368</v>
       </c>
       <c r="N22" t="n">
         <v>189</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3661</v>
+        <v>0.5284</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2135</v>
+        <v>0.3082</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4727</v>
+        <v>-0.3837</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3661</v>
+        <v>0.5284</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2981</v>
+        <v>0.4585</v>
       </c>
       <c r="G23" t="n">
-        <v>0.068</v>
+        <v>0.0699</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2981</v>
+        <v>0.4585</v>
       </c>
       <c r="I23" t="n">
-        <v>0.155</v>
+        <v>0.2476</v>
       </c>
       <c r="J23" t="n">
-        <v>0.068</v>
+        <v>0.0699</v>
       </c>
       <c r="K23" t="n">
         <v>103</v>
@@ -1495,7 +1495,7 @@
         <v>78</v>
       </c>
       <c r="M23" t="n">
-        <v>0.223</v>
+        <v>0.3175</v>
       </c>
       <c r="N23" t="n">
         <v>181</v>
@@ -1504,277 +1504,277 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ofnu</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0051</v>
+        <v>0.0419</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6341</v>
+        <v>-0.5915</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="F24" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.5626</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.6344</v>
       </c>
       <c r="H24" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.5626</v>
       </c>
       <c r="I24" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.3038</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.6344</v>
       </c>
       <c r="K24" t="n">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="M24" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.3305999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>79</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0934</v>
+        <v>0.0134</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0545</v>
+        <v>0.0078</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6802</v>
+        <v>-0.6181</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0934</v>
+        <v>0.0134</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0934</v>
+        <v>-0.1613</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1747</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0934</v>
+        <v>-0.1613</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0934</v>
+        <v>-0.0871</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.1747</v>
       </c>
       <c r="K25" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0934</v>
+        <v>0.0876</v>
       </c>
       <c r="N25" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>ofnu</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1018</v>
+        <v>-0.0557</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0594</v>
+        <v>-0.0325</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6496</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1018</v>
+        <v>-0.0557</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1018</v>
+        <v>-0.0557</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1018</v>
+        <v>-0.0557</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1018</v>
+        <v>-0.0557</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1018</v>
+        <v>-0.0557</v>
       </c>
       <c r="N26" t="n">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1056</v>
+        <v>-0.1599</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0616</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6857</v>
+        <v>-0.697</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1056</v>
+        <v>-0.1599</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2406</v>
+        <v>-0.1599</v>
       </c>
       <c r="G27" t="n">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2406</v>
+        <v>-0.1599</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1251</v>
+        <v>-0.1599</v>
       </c>
       <c r="J27" t="n">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="L27" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.00990000000000002</v>
+        <v>-0.1599</v>
       </c>
       <c r="N27" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2006</v>
+        <v>-0.1773</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.117</v>
+        <v>-0.1034</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7286</v>
+        <v>-0.7049</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2006</v>
+        <v>-0.1773</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2006</v>
+        <v>-0.1773</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2006</v>
+        <v>-0.1773</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2006</v>
+        <v>-0.1773</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2006</v>
+        <v>-0.1773</v>
       </c>
       <c r="N28" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.246</v>
+        <v>-0.2117</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1435</v>
+        <v>-0.1235</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7491</v>
+        <v>-0.7206</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.246</v>
+        <v>-0.2117</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7474</v>
+        <v>-0.2117</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5014</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7474</v>
+        <v>-0.2117</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3886</v>
+        <v>-0.2117</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5014</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="L29" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1128</v>
+        <v>-0.2117</v>
       </c>
       <c r="N29" t="n">
-        <v>189</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.309</v>
+        <v>-0.3419</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1802</v>
+        <v>-0.1994</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7775</v>
+        <v>-0.7798</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.309</v>
+        <v>-0.3419</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.309</v>
+        <v>-0.3419</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.309</v>
+        <v>-0.3419</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.309</v>
+        <v>-0.3419</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.309</v>
+        <v>-0.3419</v>
       </c>
       <c r="N30" t="n">
         <v>113</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3649</v>
+        <v>-0.4223</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2128</v>
+        <v>-0.2463</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8027</v>
+        <v>-0.8164</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3649</v>
+        <v>-0.4223</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3649</v>
+        <v>-0.4223</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3649</v>
+        <v>-0.4223</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3649</v>
+        <v>-0.4223</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3649</v>
+        <v>-0.4223</v>
       </c>
       <c r="N31" t="n">
         <v>79</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RaZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6726</v>
+        <v>-0.6156</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3923</v>
+        <v>-0.3591</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9417</v>
+        <v>-0.9044</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6726</v>
+        <v>-0.6156</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6726</v>
+        <v>-0.3713</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.2443</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6726</v>
+        <v>-0.3713</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6726</v>
+        <v>-0.2005</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.2443</v>
       </c>
       <c r="K32" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6726</v>
+        <v>-0.4448</v>
       </c>
       <c r="N32" t="n">
-        <v>79</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6879</v>
+        <v>-0.7044</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4013</v>
+        <v>-0.4109</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9486</v>
+        <v>-0.9449</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6879</v>
+        <v>-0.7044</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6879</v>
+        <v>-0.7044</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6879</v>
+        <v>-0.7044</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6879</v>
+        <v>-0.7044</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6879</v>
+        <v>-0.7044</v>
       </c>
       <c r="N33" t="n">
         <v>97</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>RaZ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7099</v>
+        <v>-0.731</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4141</v>
+        <v>-0.4264</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9585</v>
+        <v>-0.957</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7099</v>
+        <v>-0.731</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4775</v>
+        <v>-0.731</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2324</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4775</v>
+        <v>-0.731</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2483</v>
+        <v>-0.731</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2324</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="L34" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4807</v>
+        <v>-0.731</v>
       </c>
       <c r="N34" t="n">
-        <v>126</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8349</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.487</v>
+        <v>-0.5189</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0149</v>
+        <v>-1.0292</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8349</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8349</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8349</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8349</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8349</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>79</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9664</v>
+        <v>-1.0273</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5637</v>
+        <v>-0.5992</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0743</v>
+        <v>-1.0919</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9664</v>
+        <v>-1.0273</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9664</v>
+        <v>-1.0273</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9664</v>
+        <v>-1.0273</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9664</v>
+        <v>-1.0273</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9664</v>
+        <v>-1.0273</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0948</v>
+        <v>-1.1309</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.6597</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1323</v>
+        <v>-1.139</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0948</v>
+        <v>-1.1309</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0948</v>
+        <v>-1.1309</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0948</v>
+        <v>-1.1309</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0948</v>
+        <v>-1.1309</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0948</v>
+        <v>-1.1309</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.318</v>
+        <v>-1.3352</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7688</v>
+        <v>-0.7788</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.233</v>
+        <v>-1.232</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.318</v>
+        <v>-1.3352</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.318</v>
+        <v>-1.3352</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.318</v>
+        <v>-1.3352</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.318</v>
+        <v>-1.3352</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.318</v>
+        <v>-1.3352</v>
       </c>
       <c r="N38" t="n">
         <v>97</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4533</v>
+        <v>-1.4677</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8477</v>
+        <v>-0.8561</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2941</v>
+        <v>-1.2923</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4533</v>
+        <v>-1.4677</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4533</v>
+        <v>-1.4677</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4533</v>
+        <v>-1.4677</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4533</v>
+        <v>-1.4677</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4533</v>
+        <v>-1.4677</v>
       </c>
       <c r="N39" t="n">
         <v>132</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8728</v>
+        <v>-1.8621</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.0924</v>
+        <v>-1.0862</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4835</v>
+        <v>-1.4719</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8728</v>
+        <v>-1.8621</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8728</v>
+        <v>-1.8621</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8728</v>
+        <v>-1.8621</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.8728</v>
+        <v>-1.8621</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8728</v>
+        <v>-1.8621</v>
       </c>
       <c r="N40" t="n">
         <v>132</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0515</v>
+        <v>-2.1371</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.1966</v>
+        <v>-1.2466</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5642</v>
+        <v>-1.5971</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0515</v>
+        <v>-2.1371</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.1206</v>
+        <v>-0.1737</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.9309</v>
+        <v>-1.9634</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.1206</v>
+        <v>-0.1737</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.9309</v>
+        <v>-1.9634</v>
       </c>
       <c r="K41" t="n">
         <v>177</v>
@@ -2323,7 +2323,7 @@
         <v>156</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9936</v>
+        <v>-2.0572</v>
       </c>
       <c r="N41" t="n">
         <v>333</v>
@@ -2429,10 +2429,10 @@
         <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>0.374</v>
+        <v>0.3713</v>
       </c>
       <c r="J2" t="n">
-        <v>9.35</v>
+        <v>9.282500000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>0.065</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.625</v>
+        <v>1.7025</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2088</v>
+        <v>-0.2246</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.22</v>
+        <v>-5.615</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2189</v>
+        <v>-0.2346</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.4725</v>
+        <v>-5.865</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3071</v>
+        <v>-0.3212</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.6775</v>
+        <v>-8.029999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4404</v>
+        <v>0.4468</v>
       </c>
       <c r="J7" t="n">
-        <v>11.01</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.27</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3913</v>
+        <v>0.4002</v>
       </c>
       <c r="J8" t="n">
-        <v>9.782500000000001</v>
+        <v>10.005</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1395</v>
+        <v>0.1531</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4875</v>
+        <v>3.8275</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.193</v>
+        <v>-0.2054</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.825</v>
+        <v>-5.135</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.71</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3316</v>
+        <v>-0.3422</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.289999999999999</v>
+        <v>-8.555</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.08</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2978</v>
+        <v>0.293</v>
       </c>
       <c r="J12" t="n">
-        <v>8.0406</v>
+        <v>7.911</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.03</v>
       </c>
       <c r="I13" t="n">
-        <v>0.136</v>
+        <v>0.1395</v>
       </c>
       <c r="J13" t="n">
-        <v>3.672</v>
+        <v>3.7665</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.099</v>
+        <v>0.1032</v>
       </c>
       <c r="J14" t="n">
-        <v>2.673</v>
+        <v>2.7864</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1592</v>
+        <v>-0.1653</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.2984</v>
+        <v>-4.4631</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.5827</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.5888</v>
+        <v>-15.7329</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.426</v>
+        <v>0.4172</v>
       </c>
       <c r="J17" t="n">
-        <v>11.502</v>
+        <v>11.2644</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.97</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0443</v>
+        <v>-0.0539</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1961</v>
+        <v>-1.4553</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.85</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1798</v>
+        <v>-0.1951</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.8546</v>
+        <v>-5.2677</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.85</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1798</v>
+        <v>-0.1951</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.8546</v>
+        <v>-5.2677</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2306</v>
+        <v>-0.2459</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.2262</v>
+        <v>-6.6393</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.313</v>
+        <v>1.3822</v>
       </c>
       <c r="J22" t="n">
-        <v>30.199</v>
+        <v>31.7906</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2887</v>
+        <v>0.294</v>
       </c>
       <c r="J23" t="n">
-        <v>6.6401</v>
+        <v>6.762</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1351</v>
+        <v>0.1489</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1073</v>
+        <v>3.4247</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1005</v>
+        <v>0.1153</v>
       </c>
       <c r="J25" t="n">
-        <v>2.3115</v>
+        <v>2.6519</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.9</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.387</v>
+        <v>-0.3685</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.901</v>
+        <v>-8.4755</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.07</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2693</v>
+        <v>0.2544</v>
       </c>
       <c r="J27" t="n">
-        <v>6.1939</v>
+        <v>5.8512</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.92</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0819</v>
+        <v>-0.1007</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.8837</v>
+        <v>-2.3161</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2782</v>
+        <v>-0.2969</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.3986</v>
+        <v>-6.8287</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2971</v>
+        <v>-0.3153</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.8333</v>
+        <v>-7.2519</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5581</v>
+        <v>-0.5629</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.8363</v>
+        <v>-12.9467</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.56</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5372</v>
+        <v>0.6157</v>
       </c>
       <c r="J32" t="n">
-        <v>11.2812</v>
+        <v>12.9297</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.3</v>
       </c>
       <c r="I33" t="n">
-        <v>0.369</v>
+        <v>0.4084</v>
       </c>
       <c r="J33" t="n">
-        <v>7.749</v>
+        <v>8.5764</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.341</v>
+        <v>0.3648</v>
       </c>
       <c r="J34" t="n">
-        <v>7.161</v>
+        <v>7.6608</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.13</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1882</v>
+        <v>0.2077</v>
       </c>
       <c r="J35" t="n">
-        <v>3.9522</v>
+        <v>4.3617</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.98</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0601</v>
+        <v>-0.0614</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.2621</v>
+        <v>-1.2894</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4339</v>
+        <v>0.4689</v>
       </c>
       <c r="J37" t="n">
-        <v>9.1119</v>
+        <v>9.8469</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.71</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2952</v>
+        <v>-0.3138</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.1992</v>
+        <v>-6.5898</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.66</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3422</v>
+        <v>-0.3592</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.1862</v>
+        <v>-7.5432</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3985</v>
+        <v>-0.413</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.368499999999999</v>
+        <v>-8.673</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4265</v>
+        <v>-0.4396</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.9565</v>
+        <v>-9.2316</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.72</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2739</v>
+        <v>-0.2957</v>
       </c>
       <c r="J42" t="n">
-        <v>-6.0258</v>
+        <v>-6.5054</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.71</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2836</v>
+        <v>-0.305</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.2392</v>
+        <v>-6.71</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.66</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.329</v>
+        <v>-0.3491</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.238</v>
+        <v>-7.6802</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.64</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3469</v>
+        <v>-0.3663</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.6318</v>
+        <v>-8.0586</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3836</v>
+        <v>-0.4014</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.4392</v>
+        <v>-8.8308</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.64</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0285</v>
+        <v>1.1313</v>
       </c>
       <c r="J47" t="n">
-        <v>22.627</v>
+        <v>24.8886</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.37</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6882</v>
+        <v>0.765</v>
       </c>
       <c r="J48" t="n">
-        <v>15.1404</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.23</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5037</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>11.0814</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.21</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4757</v>
+        <v>0.5285</v>
       </c>
       <c r="J50" t="n">
-        <v>10.4654</v>
+        <v>11.627</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5837</v>
+        <v>-0.5411</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.8414</v>
+        <v>-11.9042</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.9</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1172</v>
+        <v>-0.1339</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.4536</v>
+        <v>-5.0882</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.89</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1283</v>
+        <v>-0.1453</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.8754</v>
+        <v>-5.5214</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.86</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1603</v>
+        <v>-0.1777</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.0914</v>
+        <v>-6.7526</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1898</v>
+        <v>-0.2077</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.2124</v>
+        <v>-7.8926</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3156</v>
+        <v>-0.3315</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.9928</v>
+        <v>-12.597</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6782</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>25.7716</v>
+        <v>28.405</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5231</v>
+        <v>0.5767</v>
       </c>
       <c r="J58" t="n">
-        <v>19.8778</v>
+        <v>21.9146</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3207</v>
+        <v>0.3236</v>
       </c>
       <c r="J59" t="n">
-        <v>12.1866</v>
+        <v>12.2968</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0798</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.0324</v>
+        <v>-2.9184</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4365</v>
+        <v>-0.4155</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.587</v>
+        <v>-15.789</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1345</v>
+        <v>0.1366</v>
       </c>
       <c r="J62" t="n">
-        <v>3.6315</v>
+        <v>3.6882</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0217</v>
+        <v>-0.0318</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.5859</v>
+        <v>-0.8586</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0994</v>
+        <v>-0.1143</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.6838</v>
+        <v>-3.0861</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2431</v>
+        <v>-0.2598</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.5637</v>
+        <v>-7.0146</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.63</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3866</v>
+        <v>-0.3989</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.4382</v>
+        <v>-10.7703</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4878</v>
+        <v>0.5535</v>
       </c>
       <c r="J67" t="n">
-        <v>13.1706</v>
+        <v>14.9445</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0906</v>
+        <v>0.1036</v>
       </c>
       <c r="J68" t="n">
-        <v>2.4462</v>
+        <v>2.7972</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0072</v>
+        <v>-0.0055</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.1944</v>
+        <v>-0.1485</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0283</v>
+        <v>-0.0312</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.7641</v>
+        <v>-0.8424</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.93</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.109</v>
+        <v>-0.1185</v>
       </c>
       <c r="J71" t="n">
-        <v>-2.943</v>
+        <v>-3.1995</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7752</v>
+        <v>0.8498</v>
       </c>
       <c r="J72" t="n">
-        <v>20.1552</v>
+        <v>22.0948</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.6349</v>
       </c>
       <c r="J73" t="n">
-        <v>15.0306</v>
+        <v>16.5074</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.21</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5046</v>
+        <v>0.5534</v>
       </c>
       <c r="J74" t="n">
-        <v>13.1196</v>
+        <v>14.3884</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.84</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5319</v>
+        <v>-0.5047</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.8294</v>
+        <v>-13.1222</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2003</v>
+        <v>-1.0879</v>
       </c>
       <c r="J76" t="n">
-        <v>-31.2078</v>
+        <v>-28.2854</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3783</v>
+        <v>0.4009</v>
       </c>
       <c r="J77" t="n">
-        <v>9.835800000000001</v>
+        <v>10.4234</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.03</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1093</v>
+        <v>0.1126</v>
       </c>
       <c r="J78" t="n">
-        <v>2.8418</v>
+        <v>2.9276</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0533</v>
+        <v>0.0545</v>
       </c>
       <c r="J79" t="n">
-        <v>1.3858</v>
+        <v>1.417</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.73</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2985</v>
+        <v>-0.3127</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.761</v>
+        <v>-8.1302</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.68</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3462</v>
+        <v>-0.3589</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.001200000000001</v>
+        <v>-9.3314</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.8</v>
       </c>
       <c r="I82" t="n">
-        <v>1.242</v>
+        <v>1.3534</v>
       </c>
       <c r="J82" t="n">
-        <v>31.05</v>
+        <v>33.835</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5778</v>
+        <v>0.6412</v>
       </c>
       <c r="J83" t="n">
-        <v>14.445</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.01</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0068</v>
+        <v>0.0266</v>
       </c>
       <c r="J84" t="n">
-        <v>0.17</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.96</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2165</v>
+        <v>-0.205</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.4125</v>
+        <v>-5.125</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2822</v>
+        <v>-0.2674</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.055</v>
+        <v>-6.685</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5853</v>
+        <v>0.6389</v>
       </c>
       <c r="J87" t="n">
-        <v>14.6325</v>
+        <v>15.9725</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.73</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.282</v>
+        <v>-0.2998</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.05</v>
+        <v>-7.495</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.68</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3295</v>
+        <v>-0.3459</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.237500000000001</v>
+        <v>-8.647500000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3672</v>
+        <v>-0.3821</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.18</v>
+        <v>-9.5525</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3766</v>
+        <v>-0.3911</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.414999999999999</v>
+        <v>-9.7775</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.42</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8927</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>23.2102</v>
+        <v>21.6892</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.92</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1141</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.5766</v>
+        <v>-2.9666</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.91</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1106</v>
+        <v>-0.1259</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.8756</v>
+        <v>-3.2734</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4512</v>
+        <v>-0.4605</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.7312</v>
+        <v>-11.973</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.54</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4696</v>
+        <v>-0.4779</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.2096</v>
+        <v>-12.4254</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.243</v>
+        <v>1.2105</v>
       </c>
       <c r="J97" t="n">
-        <v>32.318</v>
+        <v>31.473</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.44</v>
       </c>
       <c r="I98" t="n">
-        <v>1.0745</v>
+        <v>1.0274</v>
       </c>
       <c r="J98" t="n">
-        <v>27.937</v>
+        <v>26.7124</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1335</v>
+        <v>-0.127</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.471</v>
+        <v>-3.302</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2391</v>
+        <v>-0.2294</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.2166</v>
+        <v>-5.9644</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.84</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5591</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.5366</v>
+        <v>-13.6162</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3299</v>
+        <v>0.3409</v>
       </c>
       <c r="J102" t="n">
-        <v>13.196</v>
+        <v>13.636</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.13</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2113</v>
+        <v>0.2249</v>
       </c>
       <c r="J103" t="n">
-        <v>8.452</v>
+        <v>8.996</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.96</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.067</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.68</v>
+        <v>-3.016</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0921</v>
+        <v>-0.1021</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.684</v>
+        <v>-4.084</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.0921</v>
+        <v>-0.1021</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.684</v>
+        <v>-4.084</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4439</v>
+        <v>0.4394</v>
       </c>
       <c r="J107" t="n">
-        <v>17.756</v>
+        <v>17.576</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1969</v>
+        <v>0.204</v>
       </c>
       <c r="J108" t="n">
-        <v>7.876</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2039</v>
+        <v>-0.2185</v>
       </c>
       <c r="J109" t="n">
-        <v>-8.156000000000001</v>
+        <v>-8.74</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2141</v>
+        <v>-0.2287</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.564</v>
+        <v>-9.148</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2542</v>
+        <v>-0.2684</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.168</v>
+        <v>-10.736</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.02</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1453</v>
+        <v>0.1312</v>
       </c>
       <c r="J112" t="n">
-        <v>3.1966</v>
+        <v>2.8864</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0549</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.2078</v>
+        <v>-1.6148</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1915</v>
+        <v>-0.2114</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.213</v>
+        <v>-4.6508</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4274</v>
+        <v>-0.4403</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.402799999999999</v>
+        <v>-9.6866</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.47</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5202</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.4444</v>
+        <v>-11.6094</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.5</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1223</v>
+        <v>1.0874</v>
       </c>
       <c r="J117" t="n">
-        <v>24.6906</v>
+        <v>23.9228</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.42</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0172</v>
+        <v>0.9664</v>
       </c>
       <c r="J118" t="n">
-        <v>22.3784</v>
+        <v>21.2608</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.3</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7743</v>
+        <v>0.7398</v>
       </c>
       <c r="J119" t="n">
-        <v>17.0346</v>
+        <v>16.2756</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3647</v>
+        <v>0.3719</v>
       </c>
       <c r="J120" t="n">
-        <v>8.023400000000001</v>
+        <v>8.181800000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.09</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2532</v>
+        <v>0.2693</v>
       </c>
       <c r="J121" t="n">
-        <v>5.5704</v>
+        <v>5.9246</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.71</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3951</v>
+        <v>1.3756</v>
       </c>
       <c r="J122" t="n">
-        <v>30.6922</v>
+        <v>30.2632</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.3</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7853</v>
+        <v>0.7473</v>
       </c>
       <c r="J123" t="n">
-        <v>17.2766</v>
+        <v>16.4406</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.456</v>
+        <v>0.4522</v>
       </c>
       <c r="J124" t="n">
-        <v>10.032</v>
+        <v>9.948399999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0394</v>
+        <v>0.0621</v>
       </c>
       <c r="J125" t="n">
-        <v>0.8668</v>
+        <v>1.3662</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.97</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.19</v>
+        <v>-0.1771</v>
       </c>
       <c r="J126" t="n">
-        <v>-4.18</v>
+        <v>-3.8962</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3057</v>
+        <v>0.2864</v>
       </c>
       <c r="J127" t="n">
-        <v>6.7254</v>
+        <v>6.3008</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.79</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2195</v>
+        <v>-0.2396</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.829</v>
+        <v>-5.2712</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.68</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3222</v>
+        <v>-0.3402</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.0884</v>
+        <v>-7.4844</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.66</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.341</v>
+        <v>-0.3583</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.502</v>
+        <v>-7.8826</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.54</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4533</v>
+        <v>-0.4651</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.9726</v>
+        <v>-10.2322</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1038</v>
+        <v>1.0579</v>
       </c>
       <c r="J132" t="n">
-        <v>26.4912</v>
+        <v>25.3896</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.41</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0495</v>
+        <v>0.9937</v>
       </c>
       <c r="J133" t="n">
-        <v>25.188</v>
+        <v>23.8488</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4298</v>
+        <v>0.4226</v>
       </c>
       <c r="J134" t="n">
-        <v>10.3152</v>
+        <v>10.1424</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2559</v>
+        <v>-0.249</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.1416</v>
+        <v>-5.976</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.55</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.2562</v>
+        <v>-1.1344</v>
       </c>
       <c r="J136" t="n">
-        <v>-30.1488</v>
+        <v>-27.2256</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.475</v>
+        <v>0.4604</v>
       </c>
       <c r="J137" t="n">
-        <v>11.4</v>
+        <v>11.0496</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2106</v>
+        <v>0.2112</v>
       </c>
       <c r="J138" t="n">
-        <v>5.0544</v>
+        <v>5.0688</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.78</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2472</v>
+        <v>-0.2629</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.9328</v>
+        <v>-6.3096</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2863</v>
+        <v>-0.3013</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.8712</v>
+        <v>-7.2312</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2959</v>
+        <v>-0.3107</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.1016</v>
+        <v>-7.4568</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6107</v>
+        <v>0.5677</v>
       </c>
       <c r="J142" t="n">
-        <v>13.4354</v>
+        <v>12.4894</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.88</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1223</v>
+        <v>-0.1432</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.6906</v>
+        <v>-3.1504</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.79</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2183</v>
+        <v>-0.2386</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.8026</v>
+        <v>-5.2492</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.49</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4986</v>
+        <v>-0.5079</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.9692</v>
+        <v>-11.1738</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.33</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6463</v>
+        <v>-0.6452</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.2186</v>
+        <v>-14.1944</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.49</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1286</v>
+        <v>1.0905</v>
       </c>
       <c r="J147" t="n">
-        <v>24.8292</v>
+        <v>23.991</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.31</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8165</v>
+        <v>0.7731</v>
       </c>
       <c r="J148" t="n">
-        <v>17.963</v>
+        <v>17.0082</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.7008</v>
+        <v>0.6711</v>
       </c>
       <c r="J149" t="n">
-        <v>15.4176</v>
+        <v>14.7642</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.15</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4371</v>
+        <v>0.4336</v>
       </c>
       <c r="J150" t="n">
-        <v>9.616199999999999</v>
+        <v>9.539199999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7008</v>
+        <v>-0.6482</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.4176</v>
+        <v>-14.2604</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.13</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1581</v>
+        <v>1.1593</v>
       </c>
       <c r="J152" t="n">
-        <v>27.7944</v>
+        <v>27.8232</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4068</v>
+        <v>0.4213</v>
       </c>
       <c r="J153" t="n">
-        <v>9.763199999999999</v>
+        <v>10.1112</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2425</v>
+        <v>0.261</v>
       </c>
       <c r="J154" t="n">
-        <v>5.82</v>
+        <v>6.264</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.84</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2219</v>
+        <v>-0.2304</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.3256</v>
+        <v>-5.5296</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3674</v>
+        <v>-0.3739</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.817600000000001</v>
+        <v>-8.973599999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.98</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0061</v>
+        <v>-0.0196</v>
       </c>
       <c r="J157" t="n">
-        <v>-0.1464</v>
+        <v>-0.4704</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.85</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1651</v>
+        <v>-0.1839</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.9624</v>
+        <v>-4.4136</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.82</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1958</v>
+        <v>-0.2146</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.6992</v>
+        <v>-5.1504</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2243</v>
+        <v>-0.2432</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.3832</v>
+        <v>-5.8368</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4689</v>
+        <v>-0.4789</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.2536</v>
+        <v>-11.4936</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.268</v>
+        <v>0.2682</v>
       </c>
       <c r="J162" t="n">
-        <v>7.236</v>
+        <v>7.2414</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2469</v>
+        <v>0.248</v>
       </c>
       <c r="J163" t="n">
-        <v>6.6663</v>
+        <v>6.696</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0572</v>
+        <v>-0.068</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.5444</v>
+        <v>-1.836</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1478</v>
+        <v>-0.1629</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.9906</v>
+        <v>-4.3983</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4211</v>
+        <v>-0.4308</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.3697</v>
+        <v>-11.6316</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8996</v>
+        <v>0.8354</v>
       </c>
       <c r="J167" t="n">
-        <v>24.2892</v>
+        <v>22.5558</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4986</v>
+        <v>0.4814</v>
       </c>
       <c r="J168" t="n">
-        <v>13.4622</v>
+        <v>12.9978</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3908</v>
+        <v>0.3836</v>
       </c>
       <c r="J169" t="n">
-        <v>10.5516</v>
+        <v>10.3572</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5552</v>
+        <v>-0.5262</v>
       </c>
       <c r="J170" t="n">
-        <v>-14.9904</v>
+        <v>-14.2074</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6601</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.8227</v>
+        <v>-16.7265</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.08</v>
       </c>
       <c r="I172" t="n">
-        <v>0.331</v>
+        <v>0.3052</v>
       </c>
       <c r="J172" t="n">
-        <v>7.944</v>
+        <v>7.3248</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.76</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2431</v>
+        <v>-0.264</v>
       </c>
       <c r="J173" t="n">
-        <v>-5.8344</v>
+        <v>-6.336</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2624</v>
+        <v>-0.2829</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.2976</v>
+        <v>-6.7896</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3912</v>
+        <v>-0.4073</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.3888</v>
+        <v>-9.7752</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.38</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5964</v>
+        <v>-0.5996</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.3136</v>
+        <v>-14.3904</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2336</v>
+        <v>1.2045</v>
       </c>
       <c r="J177" t="n">
-        <v>29.6064</v>
+        <v>28.908</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0693</v>
+        <v>1.0252</v>
       </c>
       <c r="J178" t="n">
-        <v>25.6632</v>
+        <v>24.6048</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3496</v>
+        <v>0.3555</v>
       </c>
       <c r="J179" t="n">
-        <v>8.3904</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1754</v>
+        <v>0.1936</v>
       </c>
       <c r="J180" t="n">
-        <v>4.2096</v>
+        <v>4.6464</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.97</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.191</v>
+        <v>-0.1778</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.584</v>
+        <v>-4.2672</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.89</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1226</v>
+        <v>-0.1409</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.3102</v>
+        <v>-3.8043</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.88</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1338</v>
+        <v>-0.1522</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.6126</v>
+        <v>-4.1094</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2156</v>
+        <v>-0.2343</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.8212</v>
+        <v>-6.3261</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.77</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2438</v>
+        <v>-0.2624</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.5826</v>
+        <v>-7.0848</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.66</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3484</v>
+        <v>-0.3641</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.4068</v>
+        <v>-9.8307</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.48</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1222</v>
+        <v>1.0822</v>
       </c>
       <c r="J187" t="n">
-        <v>30.2994</v>
+        <v>29.2194</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.24</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6601</v>
+        <v>0.6337</v>
       </c>
       <c r="J188" t="n">
-        <v>17.8227</v>
+        <v>17.1099</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3636</v>
+        <v>0.3651</v>
       </c>
       <c r="J189" t="n">
-        <v>9.8172</v>
+        <v>9.857699999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.02</v>
       </c>
       <c r="I190" t="n">
-        <v>0.0539</v>
+        <v>0.0722</v>
       </c>
       <c r="J190" t="n">
-        <v>1.4553</v>
+        <v>1.9494</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0129</v>
+        <v>0.0308</v>
       </c>
       <c r="J191" t="n">
-        <v>0.3483</v>
+        <v>0.8316</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5558</v>
+        <v>0.5132</v>
       </c>
       <c r="J192" t="n">
-        <v>11.116</v>
+        <v>10.264</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.74</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2618</v>
+        <v>-0.2824</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.236</v>
+        <v>-5.648</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.59</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3999</v>
+        <v>-0.4157</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.998</v>
+        <v>-8.314</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.54</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4466</v>
+        <v>-0.4599</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.932</v>
+        <v>-9.198</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.49</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4934</v>
+        <v>-0.5038</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.868</v>
+        <v>-10.076</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3686</v>
+        <v>1.35</v>
       </c>
       <c r="J197" t="n">
-        <v>27.372</v>
+        <v>27</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.3</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7749</v>
+        <v>0.7402</v>
       </c>
       <c r="J198" t="n">
-        <v>15.498</v>
+        <v>14.804</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5693</v>
+        <v>0.5567</v>
       </c>
       <c r="J199" t="n">
-        <v>11.386</v>
+        <v>11.134</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.15</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4186</v>
+        <v>0.4208</v>
       </c>
       <c r="J200" t="n">
-        <v>8.372</v>
+        <v>8.416</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.06</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1639</v>
+        <v>0.1856</v>
       </c>
       <c r="J201" t="n">
-        <v>3.278</v>
+        <v>3.712</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J202" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>2.24</v>
       </c>
       <c r="I203" t="n">
-        <v>1.8338</v>
+        <v>1.9016</v>
       </c>
       <c r="J203" t="n">
-        <v>29.3408</v>
+        <v>30.4256</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.71</v>
       </c>
       <c r="I204" t="n">
-        <v>1.3142</v>
+        <v>1.3046</v>
       </c>
       <c r="J204" t="n">
-        <v>21.0272</v>
+        <v>20.8736</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.28</v>
       </c>
       <c r="I205" t="n">
-        <v>0.6536</v>
+        <v>0.6474</v>
       </c>
       <c r="J205" t="n">
-        <v>10.4576</v>
+        <v>10.3584</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.72</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.9579</v>
+        <v>-0.8605</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.3264</v>
+        <v>-13.768</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.4</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.4872</v>
+        <v>-0.5117</v>
       </c>
       <c r="J207" t="n">
-        <v>-7.7952</v>
+        <v>-8.187200000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.35</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.542</v>
+        <v>-0.5611</v>
       </c>
       <c r="J208" t="n">
-        <v>-8.672000000000001</v>
+        <v>-8.977600000000001</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.35</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.542</v>
+        <v>-0.5611</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.672000000000001</v>
+        <v>-8.977600000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.31</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5798</v>
+        <v>-0.5955</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.2768</v>
+        <v>-9.528</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.21</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6889</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.0224</v>
+        <v>-11.088</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I212" t="n">
-        <v>0.162</v>
+        <v>0.1512</v>
       </c>
       <c r="J212" t="n">
-        <v>3.888</v>
+        <v>3.6288</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.8</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2144</v>
+        <v>-0.2334</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.1456</v>
+        <v>-5.6016</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2329</v>
+        <v>-0.2519</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.5896</v>
+        <v>-6.0456</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.318</v>
+        <v>-0.3352</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.632</v>
+        <v>-8.0448</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3746</v>
+        <v>-0.3895</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.990399999999999</v>
+        <v>-9.348000000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1989</v>
+        <v>1.1645</v>
       </c>
       <c r="J217" t="n">
-        <v>28.7736</v>
+        <v>27.948</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.32</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8468</v>
+        <v>0.7983</v>
       </c>
       <c r="J218" t="n">
-        <v>20.3232</v>
+        <v>19.1592</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8005</v>
+        <v>0.7578</v>
       </c>
       <c r="J219" t="n">
-        <v>19.212</v>
+        <v>18.1872</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4262</v>
+        <v>-0.4022</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.2288</v>
+        <v>-9.652799999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.83</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5908</v>
+        <v>-0.5512</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.1792</v>
+        <v>-13.2288</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.48</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9332</v>
+        <v>0.88</v>
       </c>
       <c r="J222" t="n">
-        <v>27.0628</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4295</v>
+        <v>0.4234</v>
       </c>
       <c r="J223" t="n">
-        <v>12.4555</v>
+        <v>12.2786</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.79</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2457</v>
+        <v>-0.2597</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.1253</v>
+        <v>-7.5313</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.74</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2947</v>
+        <v>-0.3079</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.5463</v>
+        <v>-8.9291</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3707</v>
+        <v>-0.3816</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.7503</v>
+        <v>-11.0664</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6499</v>
       </c>
       <c r="J227" t="n">
-        <v>20.01</v>
+        <v>18.8471</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.07</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2546</v>
+        <v>0.2558</v>
       </c>
       <c r="J228" t="n">
-        <v>7.3834</v>
+        <v>7.4182</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.99</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0571</v>
+        <v>-0.0612</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.6559</v>
+        <v>-1.7748</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2339</v>
+        <v>-0.2338</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.7831</v>
+        <v>-6.7802</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4665</v>
+        <v>-0.448</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.5285</v>
+        <v>-12.992</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.62</v>
       </c>
       <c r="I232" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J232" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.68</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2962</v>
+        <v>1.2821</v>
       </c>
       <c r="J233" t="n">
-        <v>20.7392</v>
+        <v>20.5136</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.51</v>
       </c>
       <c r="I234" t="n">
-        <v>1.1028</v>
+        <v>1.0729</v>
       </c>
       <c r="J234" t="n">
-        <v>17.6448</v>
+        <v>17.1664</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.01</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.068</v>
+        <v>-0.0259</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.088</v>
+        <v>-0.4144</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.89</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5029</v>
+        <v>-0.4563</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.0464</v>
+        <v>-7.3008</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.79</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1385</v>
+        <v>-0.1759</v>
       </c>
       <c r="J237" t="n">
-        <v>-2.216</v>
+        <v>-2.8144</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2773</v>
+        <v>-0.3071</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.4368</v>
+        <v>-4.9136</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.4</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.5401</v>
+        <v>-0.5527</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.6416</v>
+        <v>-8.8432</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.35</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5893</v>
+        <v>-0.5977</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.428800000000001</v>
+        <v>-9.5632</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.31</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6291</v>
+        <v>-0.6341</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.0656</v>
+        <v>-10.1456</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.52</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1717</v>
+        <v>1.1357</v>
       </c>
       <c r="J242" t="n">
-        <v>32.8076</v>
+        <v>31.7996</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7987</v>
+        <v>0.7565</v>
       </c>
       <c r="J243" t="n">
-        <v>22.3636</v>
+        <v>21.182</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4149</v>
+        <v>0.4125</v>
       </c>
       <c r="J244" t="n">
-        <v>11.6172</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0441</v>
+        <v>-0.0304</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.2348</v>
+        <v>-0.8512</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.95</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2459</v>
+        <v>-0.2341</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.8852</v>
+        <v>-6.5548</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.2</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5337</v>
+        <v>0.5038</v>
       </c>
       <c r="J247" t="n">
-        <v>14.9436</v>
+        <v>14.1064</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.83</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1857</v>
+        <v>-0.2046</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.1996</v>
+        <v>-5.7288</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.66</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3475</v>
+        <v>-0.3634</v>
       </c>
       <c r="J249" t="n">
-        <v>-9.73</v>
+        <v>-10.1752</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.65</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3569</v>
+        <v>-0.3724</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.9932</v>
+        <v>-10.4272</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.63</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3758</v>
+        <v>-0.3904</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.5224</v>
+        <v>-10.9312</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1615/event_1615_evp_summary.xlsx
+++ b/database/event/1615/event_1615_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1431</v>
+        <v>6.2247</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5833</v>
+        <v>3.6309</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1723</v>
+        <v>2.2299</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1431</v>
+        <v>6.2247</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8068</v>
+        <v>2.8405</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3363</v>
+        <v>3.3843</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3664</v>
+        <v>4.2218</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3578</v>
+        <v>2.3704</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3363</v>
+        <v>3.3843</v>
       </c>
       <c r="K2" t="n">
         <v>36</v>
@@ -529,7 +529,7 @@
         <v>153</v>
       </c>
       <c r="M2" t="n">
-        <v>5.694100000000001</v>
+        <v>5.7547</v>
       </c>
       <c r="N2" t="n">
         <v>189</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7417</v>
+        <v>3.7222</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1825</v>
+        <v>2.1712</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0791</v>
+        <v>1.0899</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7417</v>
+        <v>3.7222</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9734</v>
+        <v>2.9988</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7683</v>
+        <v>0.7234</v>
       </c>
       <c r="H3" t="n">
-        <v>4.916</v>
+        <v>4.8163</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6546</v>
+        <v>2.7042</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7683</v>
+        <v>0.7234</v>
       </c>
       <c r="K3" t="n">
         <v>36</v>
@@ -575,7 +575,7 @@
         <v>153</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4229</v>
+        <v>3.4276</v>
       </c>
       <c r="N3" t="n">
         <v>189</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.5914</v>
+        <v>3.5275</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0949</v>
+        <v>2.0576</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0107</v>
+        <v>1.0012</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5914</v>
+        <v>3.5275</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5001</v>
+        <v>2.5644</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0913</v>
+        <v>0.9631</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3547</v>
+        <v>3.1854</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8115</v>
+        <v>1.7885</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0913</v>
+        <v>0.9631</v>
       </c>
       <c r="K4" t="n">
         <v>177</v>
@@ -621,7 +621,7 @@
         <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9028</v>
+        <v>2.7516</v>
       </c>
       <c r="N4" t="n">
         <v>333</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4829</v>
+        <v>3.4852</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0316</v>
+        <v>2.0329</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9613</v>
+        <v>0.9819</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4829</v>
+        <v>3.4852</v>
       </c>
       <c r="F5" t="n">
-        <v>2.908</v>
+        <v>2.927</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5749</v>
+        <v>0.5582</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7003</v>
+        <v>4.5465</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5381</v>
+        <v>2.5527</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5749</v>
+        <v>0.5582</v>
       </c>
       <c r="K5" t="n">
         <v>103</v>
@@ -667,7 +667,7 @@
         <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>3.113</v>
+        <v>3.1109</v>
       </c>
       <c r="N5" t="n">
         <v>181</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9558</v>
+        <v>3.0574</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7241</v>
+        <v>1.7834</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9558</v>
+        <v>3.0574</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5541</v>
+        <v>2.6572</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4017</v>
+        <v>0.4002</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5326</v>
+        <v>3.5338</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9076</v>
+        <v>1.9841</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4017</v>
+        <v>0.4002</v>
       </c>
       <c r="K6" t="n">
         <v>177</v>
@@ -713,7 +713,7 @@
         <v>156</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3093</v>
+        <v>2.3843</v>
       </c>
       <c r="N6" t="n">
         <v>333</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4494</v>
+        <v>2.4752</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4287</v>
+        <v>1.4438</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4908</v>
+        <v>0.5218</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4494</v>
+        <v>2.4752</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5678</v>
+        <v>2.6256</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1184</v>
+        <v>-0.1504</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5778</v>
+        <v>3.4152</v>
       </c>
       <c r="I7" t="n">
-        <v>1.932</v>
+        <v>1.9175</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1184</v>
+        <v>-0.1504</v>
       </c>
       <c r="K7" t="n">
         <v>45</v>
@@ -759,7 +759,7 @@
         <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8136</v>
+        <v>1.7671</v>
       </c>
       <c r="N7" t="n">
         <v>126</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2925</v>
+        <v>2.4087</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3372</v>
+        <v>1.405</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4194</v>
+        <v>0.4915</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2925</v>
+        <v>2.4087</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9662</v>
+        <v>2.9899</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6737</v>
+        <v>-0.5812</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8923</v>
+        <v>4.7826</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6418</v>
+        <v>2.6853</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6737</v>
+        <v>-0.5812</v>
       </c>
       <c r="K8" t="n">
         <v>36</v>
@@ -805,7 +805,7 @@
         <v>153</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9681</v>
+        <v>2.1041</v>
       </c>
       <c r="N8" t="n">
         <v>189</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1583</v>
+        <v>2.2341</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2589</v>
+        <v>1.3031</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3583</v>
+        <v>0.412</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1583</v>
+        <v>2.2341</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3548</v>
+        <v>2.4392</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1965</v>
+        <v>-0.2051</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8752</v>
+        <v>2.7152</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5526</v>
+        <v>1.5245</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1965</v>
+        <v>-0.2051</v>
       </c>
       <c r="K9" t="n">
         <v>103</v>
@@ -851,7 +851,7 @@
         <v>78</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3561</v>
+        <v>1.3194</v>
       </c>
       <c r="N9" t="n">
         <v>181</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.6212</v>
+        <v>1.8069</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9456</v>
+        <v>1.054</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1138</v>
+        <v>0.2173</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6212</v>
+        <v>1.8069</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3191</v>
+        <v>2.464</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6979</v>
+        <v>-0.6571</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7575</v>
+        <v>2.8083</v>
       </c>
       <c r="I10" t="n">
-        <v>1.489</v>
+        <v>1.5768</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6979</v>
+        <v>-0.6571</v>
       </c>
       <c r="K10" t="n">
         <v>45</v>
@@ -897,7 +897,7 @@
         <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7911000000000001</v>
+        <v>0.9197</v>
       </c>
       <c r="N10" t="n">
         <v>126</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5927</v>
+        <v>1.5788</v>
       </c>
       <c r="C11" t="n">
-        <v>0.929</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1008</v>
+        <v>0.1134</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5927</v>
+        <v>1.5788</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5927</v>
+        <v>1.5788</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5927</v>
+        <v>1.5788</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5927</v>
+        <v>1.5788</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5927</v>
+        <v>1.5788</v>
       </c>
       <c r="N11" t="n">
         <v>132</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4611</v>
+        <v>1.3694</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.7988</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0409</v>
+        <v>0.018</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4611</v>
+        <v>1.3694</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4611</v>
+        <v>1.3694</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4611</v>
+        <v>1.3694</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4611</v>
+        <v>1.3694</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4611</v>
+        <v>1.3694</v>
       </c>
       <c r="N12" t="n">
         <v>132</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3882</v>
+        <v>1.2863</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8097</v>
+        <v>0.7503</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0077</v>
+        <v>-0.0198</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3882</v>
+        <v>1.2863</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3882</v>
+        <v>1.5926</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.3063</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3882</v>
+        <v>1.5926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3882</v>
+        <v>0.8942</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.3063</v>
       </c>
       <c r="K13" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3882</v>
+        <v>0.5879</v>
       </c>
       <c r="N13" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2614</v>
+        <v>1.2041</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7358</v>
+        <v>0.7024</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.05</v>
+        <v>-0.0573</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2614</v>
+        <v>1.2041</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5539</v>
+        <v>1.2041</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2925</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5539</v>
+        <v>1.2041</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8391</v>
+        <v>1.2041</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2925</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="L14" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5466</v>
+        <v>1.2041</v>
       </c>
       <c r="N14" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2494</v>
+        <v>1.1484</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7288</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0555</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2494</v>
+        <v>1.1484</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9497</v>
+        <v>1.8165</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7003</v>
+        <v>-0.6681</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9497</v>
+        <v>1.8165</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0528</v>
+        <v>1.0199</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7003</v>
+        <v>-0.6681</v>
       </c>
       <c r="K15" t="n">
         <v>103</v>
@@ -1127,7 +1127,7 @@
         <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3524999999999999</v>
+        <v>0.3518</v>
       </c>
       <c r="N15" t="n">
         <v>181</v>
@@ -1136,231 +1136,231 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1352</v>
+        <v>1.1448</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6622</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1074</v>
+        <v>-0.0843</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1352</v>
+        <v>1.1448</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2765</v>
+        <v>1.1448</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8587</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2765</v>
+        <v>1.1448</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1493</v>
+        <v>1.1448</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8587</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="L16" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.008</v>
+        <v>1.1448</v>
       </c>
       <c r="N16" t="n">
-        <v>333</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1023</v>
+        <v>0.9991</v>
       </c>
       <c r="C17" t="n">
-        <v>0.643</v>
+        <v>0.5828</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1224</v>
+        <v>-0.1507</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1023</v>
+        <v>0.9991</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1023</v>
+        <v>0.9991</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1023</v>
+        <v>0.9991</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1023</v>
+        <v>0.9991</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1023</v>
+        <v>0.9991</v>
       </c>
       <c r="N17" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0509</v>
+        <v>0.9967</v>
       </c>
       <c r="C18" t="n">
-        <v>0.613</v>
+        <v>0.5814</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1458</v>
+        <v>-0.1517</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0509</v>
+        <v>0.9967</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0509</v>
+        <v>0.192</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.8047</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0509</v>
+        <v>0.192</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0509</v>
+        <v>0.1078</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.8047</v>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0509</v>
+        <v>0.9125</v>
       </c>
       <c r="N18" t="n">
-        <v>97</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8966</v>
+        <v>0.9667</v>
       </c>
       <c r="C19" t="n">
-        <v>0.523</v>
+        <v>0.5639</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2161</v>
+        <v>-0.1654</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8966</v>
+        <v>0.9667</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0263</v>
+        <v>-0.4294</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1297</v>
+        <v>1.3961</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0263</v>
+        <v>-0.4294</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5542</v>
+        <v>-0.2411</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1297</v>
+        <v>1.3961</v>
       </c>
       <c r="K19" t="n">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="L19" t="n">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4245</v>
+        <v>1.155</v>
       </c>
       <c r="N19" t="n">
-        <v>181</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8951</v>
+        <v>0.7867</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5221</v>
+        <v>0.4589</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2167</v>
+        <v>-0.2474</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8951</v>
+        <v>0.7867</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4482</v>
+        <v>0.9573</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3432</v>
+        <v>-0.1706</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4482</v>
+        <v>0.9573</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.242</v>
+        <v>0.5375</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3432</v>
+        <v>-0.1706</v>
       </c>
       <c r="K20" t="n">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="L20" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1012</v>
+        <v>0.3669</v>
       </c>
       <c r="N20" t="n">
-        <v>333</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8086</v>
+        <v>0.7184</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4717</v>
+        <v>0.419</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2561</v>
+        <v>-0.2785</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8086</v>
+        <v>0.7184</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8086</v>
+        <v>0.7184</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8086</v>
+        <v>0.7184</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8086</v>
+        <v>0.7184</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8086</v>
+        <v>0.7184</v>
       </c>
       <c r="N21" t="n">
         <v>113</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5728</v>
+        <v>0.4268</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3341</v>
+        <v>0.249</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3635</v>
+        <v>-0.4114</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5728</v>
+        <v>0.4268</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5426</v>
+        <v>0.3863</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9698</v>
+        <v>0.0405</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5426</v>
+        <v>0.3863</v>
       </c>
       <c r="I22" t="n">
-        <v>0.833</v>
+        <v>0.2169</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9698</v>
+        <v>0.0405</v>
       </c>
       <c r="K22" t="n">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="L22" t="n">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1368</v>
+        <v>0.2574</v>
       </c>
       <c r="N22" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5284</v>
+        <v>0.3959</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3082</v>
+        <v>0.2309</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3837</v>
+        <v>-0.4254</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5284</v>
+        <v>0.3959</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4585</v>
+        <v>1.396</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0699</v>
+        <v>-1.0001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4585</v>
+        <v>1.396</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2476</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0699</v>
+        <v>-1.0001</v>
       </c>
       <c r="K23" t="n">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="L23" t="n">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3175</v>
+        <v>-0.2162999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0718</v>
+        <v>0.0436</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0419</v>
+        <v>0.0254</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5915</v>
+        <v>-0.5859</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0718</v>
+        <v>0.0436</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5626</v>
+        <v>-0.5947</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6344</v>
+        <v>0.6383</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5626</v>
+        <v>-0.5947</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3038</v>
+        <v>-0.3339</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6344</v>
+        <v>0.6383</v>
       </c>
       <c r="K24" t="n">
         <v>36</v>
@@ -1541,7 +1541,7 @@
         <v>153</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3305999999999999</v>
+        <v>0.3044</v>
       </c>
       <c r="N24" t="n">
         <v>189</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0134</v>
+        <v>0.0109</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0078</v>
+        <v>0.0064</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6181</v>
+        <v>-0.6008</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0134</v>
+        <v>0.0109</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1613</v>
+        <v>-0.1541</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1747</v>
+        <v>0.165</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1613</v>
+        <v>-0.1541</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0871</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1747</v>
+        <v>0.165</v>
       </c>
       <c r="K25" t="n">
         <v>45</v>
@@ -1587,7 +1587,7 @@
         <v>81</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0876</v>
+        <v>0.07850000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>126</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0557</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0325</v>
+        <v>-0.0465</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6496</v>
+        <v>-0.6421</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0557</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0557</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0557</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0557</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0557</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>79</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1599</v>
+        <v>-0.1523</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0888</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.697</v>
+        <v>-0.6752</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1599</v>
+        <v>-0.1523</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1599</v>
+        <v>-0.1523</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1599</v>
+        <v>-0.1523</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1599</v>
+        <v>-0.1523</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1599</v>
+        <v>-0.1523</v>
       </c>
       <c r="N27" t="n">
         <v>113</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1773</v>
+        <v>-0.2391</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1034</v>
+        <v>-0.1395</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7049</v>
+        <v>-0.7147</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1773</v>
+        <v>-0.2391</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1773</v>
+        <v>-0.2391</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1773</v>
+        <v>-0.2391</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1773</v>
+        <v>-0.2391</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1773</v>
+        <v>-0.2391</v>
       </c>
       <c r="N28" t="n">
         <v>132</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2117</v>
+        <v>-0.2654</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1235</v>
+        <v>-0.1548</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7206</v>
+        <v>-0.7267</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2117</v>
+        <v>-0.2654</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2117</v>
+        <v>-0.2654</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2117</v>
+        <v>-0.2654</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2117</v>
+        <v>-0.2654</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2117</v>
+        <v>-0.2654</v>
       </c>
       <c r="N29" t="n">
         <v>113</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3419</v>
+        <v>-0.3692</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1994</v>
+        <v>-0.2154</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7798</v>
+        <v>-0.774</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3419</v>
+        <v>-0.3692</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3419</v>
+        <v>-0.3692</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3419</v>
+        <v>-0.3692</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3419</v>
+        <v>-0.3692</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3419</v>
+        <v>-0.3692</v>
       </c>
       <c r="N30" t="n">
         <v>113</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4223</v>
+        <v>-0.4277</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2463</v>
+        <v>-0.2495</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8164</v>
+        <v>-0.8006</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4223</v>
+        <v>-0.4277</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4223</v>
+        <v>-0.4277</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4223</v>
+        <v>-0.4277</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4223</v>
+        <v>-0.4277</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4223</v>
+        <v>-0.4277</v>
       </c>
       <c r="N31" t="n">
         <v>79</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6156</v>
+        <v>-0.6448</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3591</v>
+        <v>-0.3761</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9044</v>
+        <v>-0.8995</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6156</v>
+        <v>-0.6448</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3713</v>
+        <v>-0.371</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2443</v>
+        <v>-0.2738</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3713</v>
+        <v>-0.371</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2005</v>
+        <v>-0.2083</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2443</v>
+        <v>-0.2738</v>
       </c>
       <c r="K32" t="n">
         <v>45</v>
@@ -1909,7 +1909,7 @@
         <v>81</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4448</v>
+        <v>-0.4821</v>
       </c>
       <c r="N32" t="n">
         <v>126</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>RaZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7044</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4109</v>
+        <v>-0.3978</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9449</v>
+        <v>-0.9165</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7044</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7044</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7044</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7044</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7044</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RaZ</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.731</v>
+        <v>-0.7268</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4264</v>
+        <v>-0.4239</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.957</v>
+        <v>-0.9369</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.731</v>
+        <v>-0.7268</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.731</v>
+        <v>-0.7268</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.731</v>
+        <v>-0.7268</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.731</v>
+        <v>-0.7268</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.731</v>
+        <v>-0.7268</v>
       </c>
       <c r="N34" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.8442</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5189</v>
+        <v>-0.4924</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0292</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.8442</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.8442</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.8442</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.8442</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.8442</v>
       </c>
       <c r="N35" t="n">
         <v>79</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0273</v>
+        <v>-0.9655</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5992</v>
+        <v>-0.5632</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0919</v>
+        <v>-1.0456</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0273</v>
+        <v>-0.9655</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0273</v>
+        <v>-0.9655</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0273</v>
+        <v>-0.9655</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0273</v>
+        <v>-0.9655</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0273</v>
+        <v>-0.9655</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1309</v>
+        <v>-1.1161</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6597</v>
+        <v>-0.651</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.139</v>
+        <v>-1.1142</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1309</v>
+        <v>-1.1161</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1309</v>
+        <v>-1.1161</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1309</v>
+        <v>-1.1161</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1309</v>
+        <v>-1.1161</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1309</v>
+        <v>-1.1161</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3352</v>
+        <v>-1.3196</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7788</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.232</v>
+        <v>-1.2069</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3352</v>
+        <v>-1.3196</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3352</v>
+        <v>-1.3196</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3352</v>
+        <v>-1.3196</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3352</v>
+        <v>-1.3196</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3352</v>
+        <v>-1.3196</v>
       </c>
       <c r="N38" t="n">
         <v>97</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4677</v>
+        <v>-1.3813</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8561</v>
+        <v>-0.8057</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2923</v>
+        <v>-1.235</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4677</v>
+        <v>-1.3813</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4677</v>
+        <v>-1.3813</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4677</v>
+        <v>-1.3813</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4677</v>
+        <v>-1.3813</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4677</v>
+        <v>-1.3813</v>
       </c>
       <c r="N39" t="n">
         <v>132</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8621</v>
+        <v>-1.8145</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.0862</v>
+        <v>-1.0584</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4719</v>
+        <v>-1.4324</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8621</v>
+        <v>-1.8145</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8621</v>
+        <v>-1.8145</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8621</v>
+        <v>-1.8145</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.8621</v>
+        <v>-1.8145</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8621</v>
+        <v>-1.8145</v>
       </c>
       <c r="N40" t="n">
         <v>132</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1371</v>
+        <v>-2.0851</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2466</v>
+        <v>-1.2162</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5971</v>
+        <v>-1.5557</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1371</v>
+        <v>-2.0851</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.1737</v>
+        <v>-0.1909</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.9634</v>
+        <v>-1.8942</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.1737</v>
+        <v>-0.1909</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1072</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.9634</v>
+        <v>-1.8942</v>
       </c>
       <c r="K41" t="n">
         <v>177</v>
@@ -2323,7 +2323,7 @@
         <v>156</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0572</v>
+        <v>-2.0014</v>
       </c>
       <c r="N41" t="n">
         <v>333</v>
@@ -2429,10 +2429,10 @@
         <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3713</v>
+        <v>0.367</v>
       </c>
       <c r="J2" t="n">
-        <v>9.282500000000001</v>
+        <v>9.175000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0549</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7025</v>
+        <v>1.3725</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2246</v>
+        <v>-0.2045</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.615</v>
+        <v>-5.1125</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2346</v>
+        <v>-0.2146</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.865</v>
+        <v>-5.365</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3212</v>
+        <v>-0.3042</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.029999999999999</v>
+        <v>-7.605</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4468</v>
+        <v>0.3809</v>
       </c>
       <c r="J7" t="n">
-        <v>11.17</v>
+        <v>9.522500000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.27</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4002</v>
+        <v>0.3367</v>
       </c>
       <c r="J8" t="n">
-        <v>10.005</v>
+        <v>8.4175</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1531</v>
+        <v>0.1164</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8275</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2054</v>
+        <v>-0.1847</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.135</v>
+        <v>-4.6175</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.71</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3422</v>
+        <v>-0.3274</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.555</v>
+        <v>-8.185</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.08</v>
       </c>
       <c r="I12" t="n">
-        <v>0.293</v>
+        <v>0.2523</v>
       </c>
       <c r="J12" t="n">
-        <v>7.911</v>
+        <v>6.8121</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.03</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1395</v>
+        <v>0.1104</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7665</v>
+        <v>2.9808</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1032</v>
+        <v>0.0789</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7864</v>
+        <v>2.1303</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1653</v>
+        <v>-0.135</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.4631</v>
+        <v>-3.645</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5827</v>
+        <v>-0.5431</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.7329</v>
+        <v>-14.6637</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4172</v>
+        <v>0.3612</v>
       </c>
       <c r="J17" t="n">
-        <v>11.2644</v>
+        <v>9.7524</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.97</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0539</v>
+        <v>-0.0433</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4553</v>
+        <v>-1.1691</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.85</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1951</v>
+        <v>-0.1751</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.2677</v>
+        <v>-4.7277</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.85</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1951</v>
+        <v>-0.1751</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.2677</v>
+        <v>-4.7277</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2459</v>
+        <v>-0.2259</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.6393</v>
+        <v>-6.0993</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3822</v>
+        <v>1.4207</v>
       </c>
       <c r="J22" t="n">
-        <v>31.7906</v>
+        <v>32.6761</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.294</v>
+        <v>0.2599</v>
       </c>
       <c r="J23" t="n">
-        <v>6.762</v>
+        <v>5.9777</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1489</v>
+        <v>0.1241</v>
       </c>
       <c r="J24" t="n">
-        <v>3.4247</v>
+        <v>2.8543</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1153</v>
+        <v>0.094</v>
       </c>
       <c r="J25" t="n">
-        <v>2.6519</v>
+        <v>2.162</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.9</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3685</v>
+        <v>-0.3264</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.4755</v>
+        <v>-7.5072</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.07</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2544</v>
+        <v>0.2156</v>
       </c>
       <c r="J27" t="n">
-        <v>5.8512</v>
+        <v>4.9588</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.92</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1007</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.3161</v>
+        <v>-1.9895</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2969</v>
+        <v>-0.2805</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.8287</v>
+        <v>-6.4515</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3153</v>
+        <v>-0.2993</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.2519</v>
+        <v>-6.8839</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.43</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5629</v>
+        <v>-0.5707</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.9467</v>
+        <v>-13.1261</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.56</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6157</v>
+        <v>0.577</v>
       </c>
       <c r="J32" t="n">
-        <v>12.9297</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.3</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4084</v>
+        <v>0.3473</v>
       </c>
       <c r="J33" t="n">
-        <v>8.5764</v>
+        <v>7.2933</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3648</v>
+        <v>0.307</v>
       </c>
       <c r="J34" t="n">
-        <v>7.6608</v>
+        <v>6.447</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.13</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2077</v>
+        <v>0.1668</v>
       </c>
       <c r="J35" t="n">
-        <v>4.3617</v>
+        <v>3.5028</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.98</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0614</v>
+        <v>-0.0493</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.2894</v>
+        <v>-1.0353</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4689</v>
+        <v>0.5026</v>
       </c>
       <c r="J37" t="n">
-        <v>9.8469</v>
+        <v>10.5546</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.71</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3138</v>
+        <v>-0.2981</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.5898</v>
+        <v>-6.2601</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.66</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3592</v>
+        <v>-0.3452</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.5432</v>
+        <v>-7.2492</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.413</v>
+        <v>-0.4026</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.673</v>
+        <v>-8.454599999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4396</v>
+        <v>-0.4316</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.2316</v>
+        <v>-9.063599999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.72</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2957</v>
+        <v>-0.2829</v>
       </c>
       <c r="J42" t="n">
-        <v>-6.5054</v>
+        <v>-6.2238</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.71</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.305</v>
+        <v>-0.2925</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.71</v>
+        <v>-6.435</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.66</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3491</v>
+        <v>-0.3373</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.6802</v>
+        <v>-7.4206</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.64</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3663</v>
+        <v>-0.3549</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.0586</v>
+        <v>-7.8078</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.6</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4014</v>
+        <v>-0.3913</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.8308</v>
+        <v>-8.608599999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.64</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1313</v>
+        <v>1.1241</v>
       </c>
       <c r="J47" t="n">
-        <v>24.8886</v>
+        <v>24.7302</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.37</v>
       </c>
       <c r="I48" t="n">
-        <v>0.765</v>
+        <v>0.7511</v>
       </c>
       <c r="J48" t="n">
-        <v>16.83</v>
+        <v>16.5242</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.23</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5545</v>
       </c>
       <c r="J49" t="n">
-        <v>12.32</v>
+        <v>12.199</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.21</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5285</v>
+        <v>0.5228</v>
       </c>
       <c r="J50" t="n">
-        <v>11.627</v>
+        <v>11.5016</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5411</v>
+        <v>-0.5046</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.9042</v>
+        <v>-11.1012</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.9</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1339</v>
+        <v>-0.1182</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.0882</v>
+        <v>-4.4916</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.89</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1453</v>
+        <v>-0.1291</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.5214</v>
+        <v>-4.9058</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.86</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1777</v>
+        <v>-0.1604</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.7526</v>
+        <v>-6.0952</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2077</v>
+        <v>-0.1895</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.8926</v>
+        <v>-7.201</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3315</v>
+        <v>-0.3153</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.597</v>
+        <v>-11.9814</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>28.405</v>
+        <v>27.7932</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5767</v>
+        <v>0.5655</v>
       </c>
       <c r="J58" t="n">
-        <v>21.9146</v>
+        <v>21.489</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3236</v>
+        <v>0.287</v>
       </c>
       <c r="J59" t="n">
-        <v>12.2968</v>
+        <v>10.906</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.9184</v>
+        <v>-2.147</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4155</v>
+        <v>-0.3728</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.789</v>
+        <v>-14.1664</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.05</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1366</v>
+        <v>0.1204</v>
       </c>
       <c r="J62" t="n">
-        <v>3.6882</v>
+        <v>3.2508</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0318</v>
+        <v>-0.0244</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.8586</v>
+        <v>-0.6588000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1143</v>
+        <v>-0.099</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.0861</v>
+        <v>-2.673</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2598</v>
+        <v>-0.2407</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.0146</v>
+        <v>-6.4989</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.63</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3989</v>
+        <v>-0.3875</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.7703</v>
+        <v>-10.4625</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.45</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5535</v>
+        <v>0.5183</v>
       </c>
       <c r="J67" t="n">
-        <v>14.9445</v>
+        <v>13.9941</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1036</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>2.7972</v>
+        <v>2.0736</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0055</v>
+        <v>-0.0037</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.1485</v>
+        <v>-0.0999</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.99</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0312</v>
+        <v>-0.0224</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.8424</v>
+        <v>-0.6048</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.93</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1185</v>
+        <v>-0.0999</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.1995</v>
+        <v>-2.6973</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8498</v>
+        <v>0.835</v>
       </c>
       <c r="J72" t="n">
-        <v>22.0948</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6349</v>
+        <v>0.6208</v>
       </c>
       <c r="J73" t="n">
-        <v>16.5074</v>
+        <v>16.1408</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.21</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5534</v>
+        <v>0.5422</v>
       </c>
       <c r="J74" t="n">
-        <v>14.3884</v>
+        <v>14.0972</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.84</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5047</v>
+        <v>-0.4628</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.1222</v>
+        <v>-12.0328</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0879</v>
+        <v>-1.0974</v>
       </c>
       <c r="J76" t="n">
-        <v>-28.2854</v>
+        <v>-28.5324</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4009</v>
+        <v>0.3457</v>
       </c>
       <c r="J77" t="n">
-        <v>10.4234</v>
+        <v>8.988200000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.03</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1126</v>
+        <v>0.0833</v>
       </c>
       <c r="J78" t="n">
-        <v>2.9276</v>
+        <v>2.1658</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0545</v>
+        <v>0.037</v>
       </c>
       <c r="J79" t="n">
-        <v>1.417</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.73</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3127</v>
+        <v>-0.2952</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.1302</v>
+        <v>-7.6752</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.68</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3589</v>
+        <v>-0.3445</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.3314</v>
+        <v>-8.957000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.8</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3534</v>
+        <v>1.3641</v>
       </c>
       <c r="J82" t="n">
-        <v>33.835</v>
+        <v>34.1025</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6412</v>
+        <v>0.6293</v>
       </c>
       <c r="J83" t="n">
-        <v>16.03</v>
+        <v>15.7325</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.01</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0266</v>
+        <v>0.0168</v>
       </c>
       <c r="J84" t="n">
-        <v>0.665</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.96</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.205</v>
+        <v>-0.1706</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.125</v>
+        <v>-4.265</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2674</v>
+        <v>-0.2292</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.685</v>
+        <v>-5.73</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6389</v>
+        <v>0.6211</v>
       </c>
       <c r="J87" t="n">
-        <v>15.9725</v>
+        <v>15.5275</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.73</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2998</v>
+        <v>-0.2828</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.495</v>
+        <v>-7.07</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.68</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3459</v>
+        <v>-0.3307</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.647500000000001</v>
+        <v>-8.2675</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.64</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3821</v>
+        <v>-0.3692</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.5525</v>
+        <v>-9.23</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3911</v>
+        <v>-0.3789</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.7775</v>
+        <v>-9.4725</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.42</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7964</v>
       </c>
       <c r="J92" t="n">
-        <v>21.6892</v>
+        <v>20.7064</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.92</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1141</v>
+        <v>-0.0989</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.9666</v>
+        <v>-2.5714</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.91</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1259</v>
+        <v>-0.11</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.2734</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4605</v>
+        <v>-0.4555</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.973</v>
+        <v>-11.843</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.54</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4779</v>
+        <v>-0.475</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.4254</v>
+        <v>-12.35</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2105</v>
+        <v>1.2269</v>
       </c>
       <c r="J97" t="n">
-        <v>31.473</v>
+        <v>31.8994</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.44</v>
       </c>
       <c r="I98" t="n">
-        <v>1.0274</v>
+        <v>1.0291</v>
       </c>
       <c r="J98" t="n">
-        <v>26.7124</v>
+        <v>26.7566</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.127</v>
+        <v>-0.0997</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.302</v>
+        <v>-2.5922</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2294</v>
+        <v>-0.1924</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.9644</v>
+        <v>-5.0024</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.84</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.484</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.6162</v>
+        <v>-12.584</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3409</v>
+        <v>0.2816</v>
       </c>
       <c r="J102" t="n">
-        <v>13.636</v>
+        <v>11.264</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.13</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2249</v>
+        <v>0.1776</v>
       </c>
       <c r="J103" t="n">
-        <v>8.996</v>
+        <v>7.104</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.96</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0604</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.016</v>
+        <v>-2.416</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1021</v>
+        <v>-0.0847</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.084</v>
+        <v>-3.388</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1021</v>
+        <v>-0.0847</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.084</v>
+        <v>-3.388</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.27</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4394</v>
+        <v>0.4421</v>
       </c>
       <c r="J107" t="n">
-        <v>17.576</v>
+        <v>17.684</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.204</v>
+        <v>0.1871</v>
       </c>
       <c r="J108" t="n">
-        <v>8.16</v>
+        <v>7.484</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2185</v>
+        <v>-0.1981</v>
       </c>
       <c r="J109" t="n">
-        <v>-8.74</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.82</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2287</v>
+        <v>-0.2084</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.148</v>
+        <v>-8.336</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2684</v>
+        <v>-0.249</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.736</v>
+        <v>-9.960000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.02</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1312</v>
+        <v>0.1073</v>
       </c>
       <c r="J112" t="n">
-        <v>2.8864</v>
+        <v>2.3606</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0602</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.6148</v>
+        <v>-1.3244</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.82</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2114</v>
+        <v>-0.1953</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.6508</v>
+        <v>-4.2966</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4403</v>
+        <v>-0.4324</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.6866</v>
+        <v>-9.5128</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.47</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.5301</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.6094</v>
+        <v>-11.6622</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.5</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0874</v>
+        <v>1.0983</v>
       </c>
       <c r="J117" t="n">
-        <v>23.9228</v>
+        <v>24.1626</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.42</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9664</v>
+        <v>0.9601</v>
       </c>
       <c r="J118" t="n">
-        <v>21.2608</v>
+        <v>21.1222</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.3</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7398</v>
+        <v>0.7164</v>
       </c>
       <c r="J119" t="n">
-        <v>16.2756</v>
+        <v>15.7608</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3719</v>
+        <v>0.3397</v>
       </c>
       <c r="J120" t="n">
-        <v>8.181800000000001</v>
+        <v>7.4734</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.09</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2693</v>
+        <v>0.2384</v>
       </c>
       <c r="J121" t="n">
-        <v>5.9246</v>
+        <v>5.2448</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.71</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3756</v>
+        <v>1.4003</v>
       </c>
       <c r="J122" t="n">
-        <v>30.2632</v>
+        <v>30.8066</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.3</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7473</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>16.4406</v>
+        <v>15.8686</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.16</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4522</v>
+        <v>0.4189</v>
       </c>
       <c r="J124" t="n">
-        <v>9.948399999999999</v>
+        <v>9.2158</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0621</v>
+        <v>0.0459</v>
       </c>
       <c r="J125" t="n">
-        <v>1.3662</v>
+        <v>1.0098</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.97</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1771</v>
+        <v>-0.1461</v>
       </c>
       <c r="J126" t="n">
-        <v>-3.8962</v>
+        <v>-3.2142</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2864</v>
+        <v>0.248</v>
       </c>
       <c r="J127" t="n">
-        <v>6.3008</v>
+        <v>5.456</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.79</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2396</v>
+        <v>-0.2237</v>
       </c>
       <c r="J128" t="n">
-        <v>-5.2712</v>
+        <v>-4.9214</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.68</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3402</v>
+        <v>-0.3255</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.4844</v>
+        <v>-7.161</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.66</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3583</v>
+        <v>-0.3443</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.8826</v>
+        <v>-7.5746</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.54</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4651</v>
+        <v>-0.4596</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.2322</v>
+        <v>-10.1112</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.45</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0579</v>
+        <v>1.0653</v>
       </c>
       <c r="J132" t="n">
-        <v>25.3896</v>
+        <v>25.5672</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.41</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9937</v>
+        <v>0.9897</v>
       </c>
       <c r="J133" t="n">
-        <v>23.8488</v>
+        <v>23.7528</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.14</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4226</v>
+        <v>0.3829</v>
       </c>
       <c r="J134" t="n">
-        <v>10.1424</v>
+        <v>9.1896</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.249</v>
+        <v>-0.2102</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.976</v>
+        <v>-5.0448</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.55</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.1344</v>
+        <v>-1.1519</v>
       </c>
       <c r="J136" t="n">
-        <v>-27.2256</v>
+        <v>-27.6456</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4604</v>
+        <v>0.4045</v>
       </c>
       <c r="J137" t="n">
-        <v>11.0496</v>
+        <v>9.708</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2112</v>
+        <v>0.1688</v>
       </c>
       <c r="J138" t="n">
-        <v>5.0688</v>
+        <v>4.0512</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.78</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2629</v>
+        <v>-0.2436</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.3096</v>
+        <v>-5.8464</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3013</v>
+        <v>-0.2832</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.2312</v>
+        <v>-6.7968</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3107</v>
+        <v>-0.2931</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.4568</v>
+        <v>-7.0344</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.22</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5677</v>
+        <v>0.5303</v>
       </c>
       <c r="J142" t="n">
-        <v>12.4894</v>
+        <v>11.6666</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.88</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1432</v>
+        <v>-0.1278</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.1504</v>
+        <v>-2.8116</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.79</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2386</v>
+        <v>-0.223</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.2492</v>
+        <v>-4.906</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.49</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5079</v>
+        <v>-0.5074</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.1738</v>
+        <v>-11.1628</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.33</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6452</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.1944</v>
+        <v>-14.6696</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.49</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0905</v>
+        <v>1.1009</v>
       </c>
       <c r="J147" t="n">
-        <v>23.991</v>
+        <v>24.2198</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.31</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7731</v>
+        <v>0.7471</v>
       </c>
       <c r="J148" t="n">
-        <v>17.0082</v>
+        <v>16.4362</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6711</v>
+        <v>0.6402</v>
       </c>
       <c r="J149" t="n">
-        <v>14.7642</v>
+        <v>14.0844</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.15</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4336</v>
+        <v>0.399</v>
       </c>
       <c r="J150" t="n">
-        <v>9.539199999999999</v>
+        <v>8.778</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6482</v>
+        <v>-0.6158</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.2604</v>
+        <v>-13.5476</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.13</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1593</v>
+        <v>1.1317</v>
       </c>
       <c r="J152" t="n">
-        <v>27.8232</v>
+        <v>27.1608</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4213</v>
+        <v>0.3585</v>
       </c>
       <c r="J153" t="n">
-        <v>10.1112</v>
+        <v>8.603999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.261</v>
+        <v>0.2135</v>
       </c>
       <c r="J154" t="n">
-        <v>6.264</v>
+        <v>5.124</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.84</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2304</v>
+        <v>-0.2116</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.5296</v>
+        <v>-5.0784</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3739</v>
+        <v>-0.3639</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.973599999999999</v>
+        <v>-8.733599999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>0.98</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0196</v>
+        <v>-0.012</v>
       </c>
       <c r="J157" t="n">
-        <v>-0.4704</v>
+        <v>-0.288</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.85</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1839</v>
+        <v>-0.1675</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.4136</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.82</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2146</v>
+        <v>-0.1977</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.1504</v>
+        <v>-4.7448</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.79</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2432</v>
+        <v>-0.2259</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.8368</v>
+        <v>-5.4216</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4789</v>
+        <v>-0.4753</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.4936</v>
+        <v>-11.4072</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2682</v>
+        <v>0.2202</v>
       </c>
       <c r="J162" t="n">
-        <v>7.2414</v>
+        <v>5.9454</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.248</v>
+        <v>0.2017</v>
       </c>
       <c r="J163" t="n">
-        <v>6.696</v>
+        <v>5.4459</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.068</v>
+        <v>-0.0557</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.836</v>
+        <v>-1.5039</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1629</v>
+        <v>-0.1437</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.3983</v>
+        <v>-3.8799</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4308</v>
+        <v>-0.423</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.6316</v>
+        <v>-11.421</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8354</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="J167" t="n">
-        <v>22.5558</v>
+        <v>21.924</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.16</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4814</v>
+        <v>0.4396</v>
       </c>
       <c r="J168" t="n">
-        <v>12.9978</v>
+        <v>11.8692</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3836</v>
+        <v>0.3422</v>
       </c>
       <c r="J169" t="n">
-        <v>10.3572</v>
+        <v>9.2394</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5262</v>
+        <v>-0.4849</v>
       </c>
       <c r="J170" t="n">
-        <v>-14.2074</v>
+        <v>-13.0923</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5821</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.7265</v>
+        <v>-15.7167</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.08</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3052</v>
+        <v>0.2714</v>
       </c>
       <c r="J172" t="n">
-        <v>7.3248</v>
+        <v>6.5136</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.76</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.264</v>
+        <v>-0.2494</v>
       </c>
       <c r="J173" t="n">
-        <v>-6.336</v>
+        <v>-5.9856</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2829</v>
+        <v>-0.2684</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.7896</v>
+        <v>-6.4416</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4073</v>
+        <v>-0.3968</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.7752</v>
+        <v>-9.523199999999999</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.38</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5996</v>
+        <v>-0.6125</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.3904</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.58</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2045</v>
+        <v>1.2195</v>
       </c>
       <c r="J177" t="n">
-        <v>28.908</v>
+        <v>29.268</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.45</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0252</v>
+        <v>1.0271</v>
       </c>
       <c r="J178" t="n">
-        <v>24.6048</v>
+        <v>24.6504</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3555</v>
+        <v>0.3225</v>
       </c>
       <c r="J179" t="n">
-        <v>8.532</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1936</v>
+        <v>0.1658</v>
       </c>
       <c r="J180" t="n">
-        <v>4.6464</v>
+        <v>3.9792</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.97</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1778</v>
+        <v>-0.1468</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.2672</v>
+        <v>-3.5232</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.89</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1409</v>
+        <v>-0.1254</v>
       </c>
       <c r="J182" t="n">
-        <v>-3.8043</v>
+        <v>-3.3858</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.88</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1522</v>
+        <v>-0.1364</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.1094</v>
+        <v>-3.6828</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2343</v>
+        <v>-0.2169</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.3261</v>
+        <v>-5.8563</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.77</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2624</v>
+        <v>-0.2448</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.0848</v>
+        <v>-6.6096</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.66</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3641</v>
+        <v>-0.3499</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.8307</v>
+        <v>-9.4473</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.48</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0822</v>
+        <v>1.0919</v>
       </c>
       <c r="J187" t="n">
-        <v>29.2194</v>
+        <v>29.4813</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.24</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6337</v>
+        <v>0.6001</v>
       </c>
       <c r="J188" t="n">
-        <v>17.1099</v>
+        <v>16.2027</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3651</v>
+        <v>0.3303</v>
       </c>
       <c r="J189" t="n">
-        <v>9.857699999999999</v>
+        <v>8.918100000000001</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.02</v>
       </c>
       <c r="I190" t="n">
-        <v>0.0722</v>
+        <v>0.0559</v>
       </c>
       <c r="J190" t="n">
-        <v>1.9494</v>
+        <v>1.5093</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.01</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0308</v>
+        <v>0.0209</v>
       </c>
       <c r="J191" t="n">
-        <v>0.8316</v>
+        <v>0.5643</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.18</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5132</v>
+        <v>0.48</v>
       </c>
       <c r="J192" t="n">
-        <v>10.264</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.74</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2824</v>
+        <v>-0.2681</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.648</v>
+        <v>-5.362</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.59</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4157</v>
+        <v>-0.4058</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.314</v>
+        <v>-8.116</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.54</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4599</v>
+        <v>-0.4538</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.198</v>
+        <v>-9.076000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.49</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5038</v>
+        <v>-0.5026</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.076</v>
+        <v>-10.052</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>1.35</v>
+        <v>1.3722</v>
       </c>
       <c r="J197" t="n">
-        <v>27</v>
+        <v>27.444</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.3</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7402</v>
+        <v>0.7166</v>
       </c>
       <c r="J198" t="n">
-        <v>14.804</v>
+        <v>14.332</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.21</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5567</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>11.134</v>
+        <v>10.534</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.15</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4208</v>
+        <v>0.3886</v>
       </c>
       <c r="J200" t="n">
-        <v>8.416</v>
+        <v>7.772</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.06</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1856</v>
+        <v>0.1578</v>
       </c>
       <c r="J201" t="n">
-        <v>3.712</v>
+        <v>3.156</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J202" t="n">
-        <v>30.9952</v>
+        <v>31.7088</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>2.24</v>
       </c>
       <c r="I203" t="n">
-        <v>1.9016</v>
+        <v>1.9687</v>
       </c>
       <c r="J203" t="n">
-        <v>30.4256</v>
+        <v>31.4992</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.71</v>
       </c>
       <c r="I204" t="n">
-        <v>1.3046</v>
+        <v>1.332</v>
       </c>
       <c r="J204" t="n">
-        <v>20.8736</v>
+        <v>21.312</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.28</v>
       </c>
       <c r="I205" t="n">
-        <v>0.6474</v>
+        <v>0.626</v>
       </c>
       <c r="J205" t="n">
-        <v>10.3584</v>
+        <v>10.016</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.72</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8605</v>
+        <v>-0.8606</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.768</v>
+        <v>-13.7696</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.4</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.5117</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="J207" t="n">
-        <v>-8.187200000000001</v>
+        <v>-8.331200000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.35</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.5611</v>
+        <v>-0.574</v>
       </c>
       <c r="J208" t="n">
-        <v>-8.977600000000001</v>
+        <v>-9.183999999999999</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.35</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.5611</v>
+        <v>-0.574</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.977600000000001</v>
+        <v>-9.183999999999999</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.31</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5955</v>
+        <v>-0.6088</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.528</v>
+        <v>-9.7408</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.21</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.7167</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.088</v>
+        <v>-11.4672</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.03</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1512</v>
+        <v>0.122</v>
       </c>
       <c r="J212" t="n">
-        <v>3.6288</v>
+        <v>2.928</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.8</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2334</v>
+        <v>-0.2165</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.6016</v>
+        <v>-5.196</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.78</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2519</v>
+        <v>-0.2349</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.0456</v>
+        <v>-5.6376</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3352</v>
+        <v>-0.3196</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.0448</v>
+        <v>-7.6704</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3895</v>
+        <v>-0.3772</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.348000000000001</v>
+        <v>-9.0528</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1645</v>
+        <v>1.1784</v>
       </c>
       <c r="J217" t="n">
-        <v>27.948</v>
+        <v>28.2816</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.32</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7983</v>
+        <v>0.773</v>
       </c>
       <c r="J218" t="n">
-        <v>19.1592</v>
+        <v>18.552</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.3</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7578</v>
+        <v>0.73</v>
       </c>
       <c r="J219" t="n">
-        <v>18.1872</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4022</v>
+        <v>-0.3607</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.652799999999999</v>
+        <v>-8.6568</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.83</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5512</v>
+        <v>-0.513</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.2288</v>
+        <v>-12.312</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.48</v>
       </c>
       <c r="I222" t="n">
-        <v>0.88</v>
+        <v>0.836</v>
       </c>
       <c r="J222" t="n">
-        <v>25.52</v>
+        <v>24.244</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4234</v>
+        <v>0.3664</v>
       </c>
       <c r="J223" t="n">
-        <v>12.2786</v>
+        <v>10.6256</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.79</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2597</v>
+        <v>-0.24</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.5313</v>
+        <v>-6.96</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.74</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3079</v>
+        <v>-0.2902</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.9291</v>
+        <v>-8.415800000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3816</v>
+        <v>-0.3694</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.0664</v>
+        <v>-10.7126</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6499</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="J227" t="n">
-        <v>18.8471</v>
+        <v>17.7886</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.07</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2558</v>
+        <v>0.2181</v>
       </c>
       <c r="J228" t="n">
-        <v>7.4182</v>
+        <v>6.3249</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.99</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0612</v>
+        <v>-0.0441</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.7748</v>
+        <v>-1.2789</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2338</v>
+        <v>-0.1964</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.7802</v>
+        <v>-5.6956</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.448</v>
+        <v>-0.405</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.992</v>
+        <v>-11.745</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>2.62</v>
       </c>
       <c r="I232" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J232" t="n">
-        <v>30.9952</v>
+        <v>31.7088</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.68</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2821</v>
+        <v>1.3041</v>
       </c>
       <c r="J233" t="n">
-        <v>20.5136</v>
+        <v>20.8656</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.51</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0729</v>
+        <v>1.0906</v>
       </c>
       <c r="J234" t="n">
-        <v>17.1664</v>
+        <v>17.4496</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.01</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0259</v>
+        <v>-0.0424</v>
       </c>
       <c r="J235" t="n">
-        <v>-0.4144</v>
+        <v>-0.6784</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.89</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4563</v>
+        <v>-0.4264</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.3008</v>
+        <v>-6.8224</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.79</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1759</v>
+        <v>-0.1491</v>
       </c>
       <c r="J237" t="n">
-        <v>-2.8144</v>
+        <v>-2.3856</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3071</v>
+        <v>-0.2954</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.9136</v>
+        <v>-4.7264</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.4</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.5527</v>
+        <v>-0.5571</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.8432</v>
+        <v>-8.913600000000001</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.35</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5977</v>
+        <v>-0.6078</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.5632</v>
+        <v>-9.7248</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.31</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6341</v>
+        <v>-0.6498</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.1456</v>
+        <v>-10.3968</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.52</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1357</v>
+        <v>1.1485</v>
       </c>
       <c r="J242" t="n">
-        <v>31.7996</v>
+        <v>32.158</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.3</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7565</v>
+        <v>0.7289</v>
       </c>
       <c r="J243" t="n">
-        <v>21.182</v>
+        <v>20.4092</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4125</v>
+        <v>0.3773</v>
       </c>
       <c r="J244" t="n">
-        <v>11.55</v>
+        <v>10.5644</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0304</v>
+        <v>-0.0248</v>
       </c>
       <c r="J245" t="n">
-        <v>-0.8512</v>
+        <v>-0.6944</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.95</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2341</v>
+        <v>-0.1973</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.5548</v>
+        <v>-5.5244</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.2</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5038</v>
+        <v>0.4567</v>
       </c>
       <c r="J247" t="n">
-        <v>14.1064</v>
+        <v>12.7876</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.83</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2046</v>
+        <v>-0.1878</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.7288</v>
+        <v>-5.2584</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.66</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3634</v>
+        <v>-0.3492</v>
       </c>
       <c r="J249" t="n">
-        <v>-10.1752</v>
+        <v>-9.7776</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.65</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3724</v>
+        <v>-0.3589</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.4272</v>
+        <v>-10.0492</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.63</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3904</v>
+        <v>-0.3782</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.9312</v>
+        <v>-10.5896</v>
       </c>
     </row>
   </sheetData>
